--- a/analysis/kapp_vivo_vs_vitro/kapp-plots-data.xlsx
+++ b/analysis/kapp_vivo_vs_vitro/kapp-plots-data.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Flux in SC / glucose uptake ($mmol/mmol\ glc$)</t>
+          <t>Flux in SC ($mmol\ gDW^{-1}h^{-1}$)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Flux in RT / glucose uptake ($mmol/mmol\ glc$)</t>
+          <t>Flux in RT ($mmol\ gDW^{-1}h^{-1}$)</t>
         </is>
       </c>
     </row>
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008418812984382023</v>
+        <v>0.2331414597491682</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04963367558780228</v>
+        <v>0.2646303344509098</v>
       </c>
     </row>
     <row r="3">
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002215480073740939</v>
+        <v>0.06135309804308146</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01306147831136612</v>
+        <v>0.06963948031303091</v>
       </c>
     </row>
     <row r="4">
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.317650699537596e-05</v>
+        <v>0.002580328948455091</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004216935221761777</v>
+        <v>0.002248330321856891</v>
       </c>
     </row>
     <row r="5">
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="6">
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="7">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="8">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003963520963999851</v>
+        <v>0.1097614432114845</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002817152647780485</v>
+        <v>0.07801516459128094</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02327481275985413</v>
+        <v>0.1240936</v>
       </c>
     </row>
     <row r="10">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.222064229536557e-09</v>
+        <v>2e-07</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.000199046706942539</v>
+        <v>0.005512183237819582</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001173433281103724</v>
+        <v>0.006256357965772339</v>
       </c>
     </row>
     <row r="12">
@@ -616,10 +616,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.000199046706942539</v>
+        <v>0.005512183237819582</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001173433281103724</v>
+        <v>0.006256357965772339</v>
       </c>
     </row>
     <row r="13">
@@ -629,10 +629,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.003595805982781375</v>
+        <v>0.09957834404394711</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1069442165389368</v>
+        <v>0.5701911747443582</v>
       </c>
     </row>
     <row r="14">
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.003920063715808338</v>
+        <v>0.1085579853963689</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01774208789253585</v>
+        <v>0.09459494178611749</v>
       </c>
     </row>
     <row r="15">
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1981135614823109</v>
+        <v>1.056275954046187</v>
       </c>
     </row>
     <row r="16">
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.712811113831438e-08</v>
+        <v>9.13214208975166e-08</v>
       </c>
     </row>
     <row r="17">
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01020948499789219</v>
+        <v>0.282730384926176</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04620777824893978</v>
+        <v>0.2463645834695243</v>
       </c>
     </row>
     <row r="18">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02478761239746567</v>
+        <v>0.6864412059945445</v>
       </c>
       <c r="C18" t="n">
-        <v>0.338329740807838</v>
+        <v>1.803862224676159</v>
       </c>
     </row>
     <row r="19">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02478761239746567</v>
+        <v>0.6864412059945445</v>
       </c>
       <c r="C19" t="n">
-        <v>0.338329740807838</v>
+        <v>1.803862224676159</v>
       </c>
     </row>
     <row r="20">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.003595805982781375</v>
+        <v>0.09957834404394711</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1069442165389368</v>
+        <v>0.5701911747443582</v>
       </c>
     </row>
     <row r="21">
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.02987502877177634</v>
+        <v>0.8273265875868133</v>
       </c>
       <c r="C21" t="n">
-        <v>0.003855621872707742</v>
+        <v>0.0205569</v>
       </c>
     </row>
     <row r="22">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1262783759082246</v>
+        <v>3.497016140946948</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2284252153837133</v>
+        <v>1.217887662522189</v>
       </c>
     </row>
     <row r="24">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.00155723310444006</v>
+        <v>0.04312432166059504</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01013993565708552</v>
+        <v>0.05406278161887105</v>
       </c>
     </row>
     <row r="25">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7108763445185127</v>
+        <v>19.68623711794737</v>
       </c>
       <c r="C25" t="n">
-        <v>14.50562747067512</v>
+        <v>77.33920576150967</v>
       </c>
     </row>
     <row r="26">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0008519035267554192</v>
+        <v>0.02359169067678276</v>
       </c>
       <c r="C26" t="n">
-        <v>0.003855639000818878</v>
+        <v>0.02055699132142089</v>
       </c>
     </row>
     <row r="27">
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002702443458078958</v>
+        <v>0.07483853292322146</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01120490646598553</v>
+        <v>0.05974085357308522</v>
       </c>
     </row>
     <row r="28">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="29">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002702443458078958</v>
+        <v>0.07483853292322146</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01120490646598553</v>
+        <v>0.05974085357308522</v>
       </c>
     </row>
     <row r="30">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.003595805982781375</v>
+        <v>0.09957834404394711</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1069442165389368</v>
+        <v>0.5701911747443582</v>
       </c>
     </row>
     <row r="31">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.00155723310444006</v>
+        <v>0.04312432166059504</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01013993565708552</v>
+        <v>0.05406278161887105</v>
       </c>
     </row>
     <row r="33">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0008518999157233045</v>
+        <v>0.02359159067678276</v>
       </c>
       <c r="C33" t="n">
-        <v>0.003855639000818878</v>
+        <v>0.02055699132142089</v>
       </c>
     </row>
     <row r="34">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.004102237271384092</v>
+        <v>0.1136029019129157</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01946425553607749</v>
+        <v>0.1037769697962083</v>
       </c>
     </row>
     <row r="35">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="36">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0007711698215961697</v>
+        <v>0.02135593916327316</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2475709410124559</v>
+        <v>1.319966336254034</v>
       </c>
     </row>
     <row r="38">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.01772517423249019</v>
+        <v>0.4908617167927797</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5670525393933853</v>
+        <v>3.023336502360245</v>
       </c>
     </row>
     <row r="39">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0007709749134759988</v>
+        <v>0.02135054158956082</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0805634191481905</v>
+        <v>0.4295374924627556</v>
       </c>
     </row>
     <row r="40">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0007709749134759988</v>
+        <v>0.02135054158956082</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0805634191481905</v>
+        <v>0.4295374924627556</v>
       </c>
     </row>
     <row r="41">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.657296658222689</v>
+        <v>45.895373</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.02902311802295669</v>
+        <v>0.8037346969100305</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.123542779274561e-06</v>
+        <v>8.65e-05</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.006164020986813107</v>
+        <v>0.1706997</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1119509467736205</v>
+        <v>0.5968854036286571</v>
       </c>
     </row>
     <row r="46">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0004326021853802591</v>
+        <v>0.01198001489964648</v>
       </c>
       <c r="C46" t="n">
-        <v>0.001957945645262293</v>
+        <v>0.01043911829632453</v>
       </c>
     </row>
     <row r="47">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.123542779274561e-06</v>
+        <v>8.65e-05</v>
       </c>
       <c r="C47" t="n">
-        <v>1.436334567364282e-08</v>
+        <v>7.658060630078012e-08</v>
       </c>
     </row>
     <row r="48">
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.002565887881492082</v>
+        <v>0.07105691115285848</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01162722743458046</v>
+        <v>0.06199252923162489</v>
       </c>
     </row>
     <row r="49">
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.002565887881492082</v>
+        <v>0.07105691115285848</v>
       </c>
       <c r="C49" t="n">
-        <v>0.01162722743458046</v>
+        <v>0.06199252923162489</v>
       </c>
     </row>
     <row r="50">
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.00838588924061595</v>
+        <v>0.2322297053609582</v>
       </c>
       <c r="C50" t="n">
-        <v>0.03795421212467968</v>
+        <v>0.2023593</v>
       </c>
     </row>
     <row r="51">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.003088143305676557</v>
+        <v>0.08551968543970495</v>
       </c>
       <c r="C51" t="n">
-        <v>0.01397679107339364</v>
+        <v>0.0745196250831687</v>
       </c>
     </row>
     <row r="52">
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.003190818821613736</v>
+        <v>0.08836306962112112</v>
       </c>
       <c r="C52" t="n">
-        <v>0.01430009427411298</v>
+        <v>0.0762433707683751</v>
       </c>
     </row>
     <row r="53">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3859630760657816</v>
+        <v>2.057827406400877</v>
       </c>
     </row>
     <row r="54">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.00838588924061595</v>
+        <v>0.2322297053609582</v>
       </c>
       <c r="C54" t="n">
-        <v>0.03795421212467968</v>
+        <v>0.2023593</v>
       </c>
     </row>
     <row r="55">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.02583904673930591</v>
+        <v>0.7155584862740556</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2692724552354029</v>
+        <v>1.435671629059731</v>
       </c>
     </row>
     <row r="56">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3859630760657816</v>
+        <v>2.057827406400877</v>
       </c>
     </row>
     <row r="57">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C58" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="59">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2319918789387708</v>
+        <v>6.424531036153851</v>
       </c>
       <c r="C59" t="n">
-        <v>4.731368887840395</v>
+        <v>25.2260933</v>
       </c>
     </row>
     <row r="60">
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0008519035267554192</v>
+        <v>0.02359169067678276</v>
       </c>
       <c r="C60" t="n">
-        <v>0.003855639000818878</v>
+        <v>0.02055699132142089</v>
       </c>
     </row>
     <row r="61">
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C61" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="62">
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C62" t="n">
-        <v>0.003879130868285365</v>
+        <v>0.02068224218529325</v>
       </c>
     </row>
     <row r="63">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C63" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="64">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C64" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="65">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C65" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="66">
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C66" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="67">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C67" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="68">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="69">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C69" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="70">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C70" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="71">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C71" t="n">
-        <v>0.003879130868285365</v>
+        <v>0.02068224218529325</v>
       </c>
     </row>
     <row r="72">
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C72" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="73">
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.815805243158865e-05</v>
+        <v>0.0005028493753164491</v>
       </c>
       <c r="C73" t="n">
-        <v>9.324241222808881e-05</v>
+        <v>0.0004971376880859632</v>
       </c>
     </row>
     <row r="74">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.005756706703105818</v>
+        <v>0.1594199807739796</v>
       </c>
       <c r="C75" t="n">
-        <v>0.02592732170869344</v>
+        <v>0.1382359</v>
       </c>
     </row>
     <row r="76">
@@ -1448,10 +1448,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.003806921823013379</v>
+        <v>0.1054247567459718</v>
       </c>
       <c r="C76" t="n">
-        <v>0.017230052188683</v>
+        <v>0.09186493684578853</v>
       </c>
     </row>
     <row r="77">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.004239524008393639</v>
+        <v>0.1174047716456183</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0191879978339453</v>
+        <v>0.1023040551421131</v>
       </c>
     </row>
     <row r="78">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.000199046706942539</v>
+        <v>0.005512183237819582</v>
       </c>
       <c r="C78" t="n">
-        <v>0.001173433281103724</v>
+        <v>0.006256357965772339</v>
       </c>
     </row>
     <row r="79">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.02478760517540144</v>
+        <v>0.6864410059945445</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.02478760156436933</v>
+        <v>0.6864409059945445</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1981135614823109</v>
+        <v>1.056275954046187</v>
       </c>
     </row>
     <row r="81">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.914231864630612</v>
+        <v>53.01065744615926</v>
       </c>
       <c r="C81" t="n">
-        <v>3.120596730088113</v>
+        <v>16.63798915937183</v>
       </c>
     </row>
     <row r="82">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.1363079727960007</v>
+        <v>3.7747649</v>
       </c>
       <c r="C82" t="n">
-        <v>1.703349918829928</v>
+        <v>9.081698128713036</v>
       </c>
     </row>
     <row r="83">
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.001666714360091101</v>
+        <v>0.0461561766032107</v>
       </c>
       <c r="C83" t="n">
-        <v>0.01043242320440953</v>
+        <v>0.05562222843707329</v>
       </c>
     </row>
     <row r="84">
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.02478761239746567</v>
+        <v>0.6864412059945445</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5364433022901488</v>
+        <v>2.860138178722346</v>
       </c>
     </row>
     <row r="85">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.00136128914069165</v>
+        <v>0.03769806242166318</v>
       </c>
       <c r="C85" t="n">
-        <v>0.009330114189675503</v>
+        <v>0.04974508152456442</v>
       </c>
     </row>
     <row r="86">
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1.610520323186652e-06</v>
+        <v>4.46e-05</v>
       </c>
       <c r="C86" t="n">
-        <v>8.265657071541309e-06</v>
+        <v>4.406974839953329e-05</v>
       </c>
     </row>
     <row r="87">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>9.317650699537596e-05</v>
+        <v>0.002580328948455091</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0004216935221761777</v>
+        <v>0.002248330321856891</v>
       </c>
     </row>
     <row r="89">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9.317650699537596e-05</v>
+        <v>0.002580328948455091</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0004216935221761777</v>
+        <v>0.002248330321856891</v>
       </c>
     </row>
     <row r="90">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0006949479195784838</v>
+        <v>0.01924513262389191</v>
       </c>
       <c r="C90" t="n">
-        <v>0.004064675061764249</v>
+        <v>0.02167150242834904</v>
       </c>
     </row>
     <row r="91">
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.004239524008393639</v>
+        <v>0.1174047716456183</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0191879978339453</v>
+        <v>0.1023040551421131</v>
       </c>
     </row>
     <row r="92">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.01020948499789219</v>
+        <v>0.282730384926176</v>
       </c>
       <c r="C92" t="n">
-        <v>0.04620777824893978</v>
+        <v>0.2463645834695243</v>
       </c>
     </row>
     <row r="93">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.003920063715808338</v>
+        <v>0.1085579853963689</v>
       </c>
       <c r="C93" t="n">
-        <v>0.01774208789253585</v>
+        <v>0.09459494178611749</v>
       </c>
     </row>
     <row r="94">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="96">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.003190818821613736</v>
+        <v>0.08836306962112112</v>
       </c>
       <c r="C96" t="n">
-        <v>0.01430009427411298</v>
+        <v>0.0762433707683751</v>
       </c>
     </row>
     <row r="97">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.003190818821613736</v>
+        <v>0.08836306962112112</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01430009427411298</v>
+        <v>0.0762433707683751</v>
       </c>
     </row>
     <row r="98">
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.004239524008393639</v>
+        <v>0.1174047716456183</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0191879978339453</v>
+        <v>0.1023040551421131</v>
       </c>
     </row>
     <row r="99">
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.004239524008393639</v>
+        <v>0.1174047716456183</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0191879978339453</v>
+        <v>0.1023040551421131</v>
       </c>
     </row>
     <row r="100">
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0009390508825934949</v>
+        <v>0.02600505486376031</v>
       </c>
       <c r="C100" t="n">
-        <v>0.007758270919951379</v>
+        <v>0.04136453333333334</v>
       </c>
     </row>
     <row r="101">
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.005425247656134766</v>
+        <v>0.1502409140574178</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03553870011943835</v>
+        <v>0.1894805892809758</v>
       </c>
     </row>
     <row r="102">
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.002817152647780485</v>
+        <v>0.07801516459128094</v>
       </c>
       <c r="C102" t="n">
-        <v>0.02327481275985413</v>
+        <v>0.1240936</v>
       </c>
     </row>
     <row r="103">
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="104">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="105">
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.786442538400008</v>
+        <v>49.47179868863186</v>
       </c>
       <c r="C105" t="n">
-        <v>0.7706015926607298</v>
+        <v>4.1085927</v>
       </c>
     </row>
     <row r="106">
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0.08260576411240525</v>
+        <v>0.4404266</v>
       </c>
     </row>
     <row r="107">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.657296661833721</v>
+        <v>45.8953731</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.815805243158865e-05</v>
+        <v>0.0005028493753164491</v>
       </c>
       <c r="C109" t="n">
-        <v>9.324241222808881e-05</v>
+        <v>0.0004971376880859632</v>
       </c>
     </row>
     <row r="110">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.914231864630612</v>
+        <v>53.01065744615926</v>
       </c>
       <c r="C110" t="n">
-        <v>3.120596730088113</v>
+        <v>16.63798915937183</v>
       </c>
     </row>
     <row r="111">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.610520323186652e-06</v>
+        <v>4.46e-05</v>
       </c>
       <c r="C111" t="n">
-        <v>8.265657071541309e-06</v>
+        <v>4.406974839953329e-05</v>
       </c>
     </row>
     <row r="112">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.657296661833721</v>
+        <v>45.8953731</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9.375541846481231e-06</v>
+        <v>0.000259636069370235</v>
       </c>
       <c r="C113" t="n">
-        <v>4.814382715353884e-05</v>
+        <v>0.000256686955590264</v>
       </c>
     </row>
     <row r="114">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>27.6929135</v>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>5.3316691</v>
       </c>
     </row>
     <row r="115">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.07378057639758659</v>
+        <v>2.043199120158507</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.03704689355347598</v>
+        <v>1.025936418620118</v>
       </c>
       <c r="C116" t="n">
-        <v>0.481092159301484</v>
+        <v>2.5650242</v>
       </c>
     </row>
     <row r="117">
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5410761187139287</v>
+        <v>14.98397415246056</v>
       </c>
       <c r="C117" t="n">
-        <v>4.508839005031276</v>
+        <v>24.0396376</v>
       </c>
     </row>
     <row r="118">
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.008523412403054811</v>
+        <v>0.236038122402624</v>
       </c>
       <c r="C118" t="n">
-        <v>0.04376810430908695</v>
+        <v>0.2333570493103357</v>
       </c>
     </row>
     <row r="119">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0008981176057667645</v>
+        <v>0.02487149316932611</v>
       </c>
       <c r="C119" t="n">
-        <v>0.004611874117101123</v>
+        <v>0.02458898672323784</v>
       </c>
     </row>
     <row r="120">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.327260442122343e-06</v>
+        <v>3.67557086156658e-05</v>
       </c>
       <c r="C120" t="n">
-        <v>6.815541795832307e-06</v>
+        <v>3.633821359259762e-05</v>
       </c>
     </row>
     <row r="121">
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.1123573830351156</v>
+        <v>3.111503289477823</v>
       </c>
       <c r="C121" t="n">
-        <v>0.5169707173639261</v>
+        <v>2.756316799374078</v>
       </c>
     </row>
     <row r="122">
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.202465493563904</v>
+        <v>5.6068594</v>
       </c>
       <c r="C122" t="n">
-        <v>2.994904965306892</v>
+        <v>15.96784226096333</v>
       </c>
     </row>
     <row r="123">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.008195324917589725</v>
+        <v>0.2269524240472069</v>
       </c>
       <c r="C123" t="n">
-        <v>0.03967613068860557</v>
+        <v>0.21154</v>
       </c>
     </row>
     <row r="124">
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.001292765790419099</v>
+        <v>0.03580045120983524</v>
       </c>
       <c r="C124" t="n">
-        <v>0.006119486463491986</v>
+        <v>0.0326270768852685</v>
       </c>
     </row>
     <row r="125">
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2.225279209345545e-05</v>
+        <v>0.0006162446465775457</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0001142690837258693</v>
+        <v>0.0006092449427865303</v>
       </c>
     </row>
     <row r="126">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>7.222064229536557e-09</v>
+        <v>2e-07</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>7.222064229536557e-09</v>
+        <v>2e-07</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.957400624688605</v>
+        <v>26.5132126843475</v>
       </c>
       <c r="C128" t="n">
-        <v>0.5474586953670577</v>
+        <v>2.918868609614855</v>
       </c>
     </row>
     <row r="129">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.00526530787930622</v>
+        <v>0.1458117156524956</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1779045121883398</v>
+        <v>0.9485279903851448</v>
       </c>
     </row>
     <row r="131">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.09543453418146126</v>
+        <v>2.6428603</v>
       </c>
       <c r="C131" t="n">
-        <v>0.8814661912497688</v>
+        <v>4.699686054581083</v>
       </c>
     </row>
     <row r="132">
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>9.375541846481231e-06</v>
+        <v>0.000259636069370235</v>
       </c>
       <c r="C132" t="n">
-        <v>4.814382715353884e-05</v>
+        <v>0.000256686955590264</v>
       </c>
     </row>
     <row r="133">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3795869499211533</v>
+        <v>10.51186856989533</v>
       </c>
       <c r="C133" t="n">
-        <v>5.65137266812336</v>
+        <v>30.13124902721787</v>
       </c>
     </row>
     <row r="134">
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5.628761529147615</v>
+        <v>30.01069391622509</v>
       </c>
     </row>
     <row r="135">
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.005731418801432847</v>
+        <v>0.1587196851003535</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1099930011283582</v>
+        <v>0.5864462853323326</v>
       </c>
     </row>
     <row r="136">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.01772534386338556</v>
+        <v>0.490866414366492</v>
       </c>
       <c r="C136" t="n">
-        <v>0.1708940826804124</v>
+        <v>0.9111507</v>
       </c>
     </row>
     <row r="137">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1.083309634430483e-08</v>
+        <v>3e-07</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.07150824607534614</v>
+        <v>1.980271673101275</v>
       </c>
       <c r="C138" t="n">
-        <v>0.5966999719810224</v>
+        <v>3.181406802582083</v>
       </c>
     </row>
     <row r="139">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.01772534386338556</v>
+        <v>0.490866414366492</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1708940826804124</v>
+        <v>0.9111507</v>
       </c>
     </row>
     <row r="140">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.007741847848090242</v>
+        <v>0.2143943227873242</v>
       </c>
       <c r="C140" t="n">
-        <v>0.03648273228479851</v>
+        <v>0.1945138564064326</v>
       </c>
     </row>
     <row r="141">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.005078913058389469</v>
+        <v>0.1406499</v>
       </c>
       <c r="C141" t="n">
-        <v>0.2475709410124559</v>
+        <v>1.319966336254034</v>
       </c>
     </row>
     <row r="142">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.07378057639758659</v>
+        <v>2.043199120158507</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.00352724889688258</v>
+        <v>0.0976797985943397</v>
       </c>
       <c r="C144" t="n">
-        <v>0.01271163800110132</v>
+        <v>0.06777424754085769</v>
       </c>
     </row>
     <row r="145">
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C145" t="n">
-        <v>0.08260576411240525</v>
+        <v>0.4404266</v>
       </c>
     </row>
     <row r="146">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.002500454338372561</v>
+        <v>0.06924486570325107</v>
       </c>
       <c r="C146" t="n">
-        <v>4.273724959015481e-07</v>
+        <v>2.278608730588161e-06</v>
       </c>
     </row>
     <row r="147">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.03401773111689054</v>
+        <v>0.9420500852863081</v>
       </c>
       <c r="C147" t="n">
-        <v>0.6349917111396245</v>
+        <v>3.385565685039262</v>
       </c>
     </row>
     <row r="148">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0148965781711198</v>
+        <v>0.4125296507388089</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0897048560129967</v>
+        <v>0.4782766089244437</v>
       </c>
     </row>
     <row r="149">
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.850474591964506</v>
+        <v>51.24503280922085</v>
       </c>
       <c r="C149" t="n">
-        <v>1.330107066028984</v>
+        <v>7.091690743638393</v>
       </c>
     </row>
     <row r="150">
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C150" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="151">
@@ -2423,10 +2423,10 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.000199046706942539</v>
+        <v>0.005512183237819582</v>
       </c>
       <c r="C151" t="n">
-        <v>0.001173433281103724</v>
+        <v>0.006256357965772339</v>
       </c>
     </row>
     <row r="152">
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.08079998695667542</v>
+        <v>2.237587049592341</v>
       </c>
       <c r="C152" t="n">
-        <v>0.6438243941716475</v>
+        <v>3.432658628231193</v>
       </c>
     </row>
     <row r="153">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.02717010881089764</v>
+        <v>0.7524194730857763</v>
       </c>
       <c r="C153" t="n">
-        <v>0.2162504259148982</v>
+        <v>1.152975713712302</v>
       </c>
     </row>
     <row r="154">
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.001399793813305135</v>
+        <v>0.03876436898969426</v>
       </c>
       <c r="C154" t="n">
-        <v>0.008259337747698358</v>
+        <v>0.04403605585586694</v>
       </c>
     </row>
     <row r="155">
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>1.132239361590758e-08</v>
+        <v>6.036725617997174e-08</v>
       </c>
     </row>
     <row r="156">
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>27.6929135</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>5.3316691</v>
       </c>
     </row>
     <row r="157">
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.03773529843438601</v>
+        <v>1.045000355440137</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1170545447740886</v>
+        <v>0.6240960993865745</v>
       </c>
     </row>
     <row r="158">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.002500454338372561</v>
+        <v>0.06924486570325107</v>
       </c>
       <c r="C158" t="n">
-        <v>4.273724959015481e-07</v>
+        <v>2.278608730588161e-06</v>
       </c>
     </row>
     <row r="159">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.003963520963999851</v>
+        <v>0.1097614432114845</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.1234312058529459</v>
+        <v>3.418169706886323</v>
       </c>
       <c r="C161" t="n">
-        <v>0.8874085044633977</v>
+        <v>4.73136850232471</v>
       </c>
     </row>
     <row r="162">
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C162" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="163">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.01342642405610374</v>
+        <v>0.3718168</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.02137349686951501</v>
+        <v>0.5918944</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1146691159587535</v>
+        <v>0.6113777822816027</v>
       </c>
     </row>
     <row r="165">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.04489545267428319</v>
+        <v>1.243285887452268</v>
       </c>
       <c r="C166" t="n">
-        <v>0.3871445085953106</v>
+        <v>2.064126413712302</v>
       </c>
     </row>
     <row r="167">
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.004058833030969811</v>
+        <v>0.1124009120375898</v>
       </c>
       <c r="C167" t="n">
-        <v>0.01702515090022532</v>
+        <v>0.09077247097756851</v>
       </c>
     </row>
     <row r="168">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.07206556148518085</v>
+        <v>1.995705360538045</v>
       </c>
       <c r="C169" t="n">
-        <v>0.6033949345102086</v>
+        <v>3.217102127424603</v>
       </c>
     </row>
     <row r="170">
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.001399793813305135</v>
+        <v>0.03876436898969426</v>
       </c>
       <c r="C170" t="n">
-        <v>0.008259349070091975</v>
+        <v>0.04403611622312312</v>
       </c>
     </row>
     <row r="171">
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.03401773111689054</v>
+        <v>0.9420500852863081</v>
       </c>
       <c r="C171" t="n">
-        <v>0.6349917111396245</v>
+        <v>3.385565685039262</v>
       </c>
     </row>
     <row r="172">
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.0009390508825934949</v>
+        <v>0.02600505486376031</v>
       </c>
       <c r="C172" t="n">
-        <v>0.007758270919951377</v>
+        <v>0.04136453333333333</v>
       </c>
     </row>
     <row r="173">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.5410761187139287</v>
+        <v>14.98397415246056</v>
       </c>
       <c r="C173" t="n">
-        <v>4.508839005031276</v>
+        <v>24.0396376</v>
       </c>
     </row>
     <row r="174">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.8541624608966016</v>
+        <v>23.65424714455672</v>
       </c>
       <c r="C174" t="n">
-        <v>18.55326846943805</v>
+        <v>98.91988820250717</v>
       </c>
     </row>
     <row r="175">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="176">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="177">
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="178">
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.1000437927919719</v>
+        <v>2.7705041</v>
       </c>
       <c r="C178" t="n">
-        <v>0.3788899543883595</v>
+        <v>2.020115862112826</v>
       </c>
     </row>
     <row r="179">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>1</v>
+        <v>27.6929135</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>5.3316691</v>
       </c>
     </row>
     <row r="181">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="182">
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C182" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="183">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C183" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="184">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.002817152647780485</v>
+        <v>0.07801516459128094</v>
       </c>
       <c r="C184" t="n">
-        <v>0.02327481275985413</v>
+        <v>0.1240936</v>
       </c>
     </row>
     <row r="185">
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.002817152647780485</v>
+        <v>0.07801516459128094</v>
       </c>
       <c r="C185" t="n">
-        <v>0.02327481275985413</v>
+        <v>0.1240936</v>
       </c>
     </row>
     <row r="186">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.008385885629583836</v>
+        <v>0.2322296053609582</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C187" t="n">
-        <v>0.03795421212467968</v>
+        <v>0.2023593</v>
       </c>
     </row>
     <row r="188">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.0008519035267554192</v>
+        <v>0.02359169067678276</v>
       </c>
       <c r="C188" t="n">
-        <v>0.003855639000818878</v>
+        <v>0.02055699132142089</v>
       </c>
     </row>
     <row r="189">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.007533985713860533</v>
+        <v>0.2086380146841755</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0340985731238608</v>
+        <v>0.1818023086785791</v>
       </c>
     </row>
     <row r="190">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C190" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="191">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.05376563087412052</v>
+        <v>1.488926965069949</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.1661565724769233</v>
+        <v>4.601359589059918</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C193" t="n">
-        <v>0.338329740807838</v>
+        <v>1.803862224676159</v>
       </c>
     </row>
     <row r="194">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.222064229536557e-09</v>
+        <v>2e-07</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
@@ -3008,10 +3008,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C196" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="197">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C197" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="198">
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.006164020986813107</v>
+        <v>0.1706997</v>
       </c>
       <c r="C198" t="n">
-        <v>0.1119509467736205</v>
+        <v>0.5968854036286571</v>
       </c>
     </row>
     <row r="199">
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.003920063715808338</v>
+        <v>0.1085579853963689</v>
       </c>
       <c r="C199" t="n">
-        <v>0.01774208789253585</v>
+        <v>0.09459494178611749</v>
       </c>
     </row>
     <row r="200">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.003920063715808338</v>
+        <v>0.1085579853963689</v>
       </c>
       <c r="C200" t="n">
-        <v>0.01774208789253585</v>
+        <v>0.09459494178611749</v>
       </c>
     </row>
     <row r="201">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.004102237271384092</v>
+        <v>0.1136029019129157</v>
       </c>
       <c r="C201" t="n">
-        <v>0.01946425553607749</v>
+        <v>0.1037769697962083</v>
       </c>
     </row>
     <row r="202">
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.001399793813305135</v>
+        <v>0.03876436898969426</v>
       </c>
       <c r="C202" t="n">
-        <v>0.008259349070091975</v>
+        <v>0.04403611622312312</v>
       </c>
     </row>
     <row r="203">
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.0009390508825934949</v>
+        <v>0.02600505486376031</v>
       </c>
       <c r="C203" t="n">
-        <v>0.007758270919951379</v>
+        <v>0.04136453333333334</v>
       </c>
     </row>
     <row r="204">
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.005331026284536014</v>
+        <v>0.1476316497638822</v>
       </c>
       <c r="C204" t="n">
-        <v>0.02412803303793936</v>
+        <v>0.1286426881921604</v>
       </c>
     </row>
     <row r="205">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.005331026284536014</v>
+        <v>0.1476316497638822</v>
       </c>
       <c r="C205" t="n">
-        <v>0.02412803303793936</v>
+        <v>0.1286426881921604</v>
       </c>
     </row>
     <row r="206">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.005331026284536014</v>
+        <v>0.1476316497638822</v>
       </c>
       <c r="C206" t="n">
-        <v>0.02412803303793936</v>
+        <v>0.1286426881921604</v>
       </c>
     </row>
     <row r="207">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.005331026284536014</v>
+        <v>0.1476316497638822</v>
       </c>
       <c r="C207" t="n">
-        <v>0.02412803303793936</v>
+        <v>0.1286426881921604</v>
       </c>
     </row>
     <row r="208">
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.01020948499789219</v>
+        <v>0.282730384926176</v>
       </c>
       <c r="C208" t="n">
-        <v>0.04620777824893978</v>
+        <v>0.2463645834695243</v>
       </c>
     </row>
     <row r="209">
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.003920063715808338</v>
+        <v>0.1085579853963689</v>
       </c>
       <c r="C209" t="n">
-        <v>0.01774208789253585</v>
+        <v>0.09459494178611749</v>
       </c>
     </row>
     <row r="210">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>0.04376810430908695</v>
+        <v>0.2333570493103357</v>
       </c>
     </row>
     <row r="211">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.008523412403054811</v>
+        <v>0.236038122402624</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.005731418801432847</v>
+        <v>0.1587196851003535</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1099930011283582</v>
+        <v>0.5864462853323326</v>
       </c>
     </row>
     <row r="213">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C213" t="n">
-        <v>0.00645826064583912</v>
+        <v>0.03443330872516648</v>
       </c>
     </row>
     <row r="214">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C214" t="n">
-        <v>0.00645826064583912</v>
+        <v>0.03443330872516648</v>
       </c>
     </row>
     <row r="215">
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>0.0226111389757438</v>
+        <v>0.1205551109927789</v>
       </c>
     </row>
     <row r="216">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>0.0226111389757438</v>
+        <v>0.1205551109927789</v>
       </c>
     </row>
     <row r="217">
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.005331026284536014</v>
+        <v>0.1476316497638822</v>
       </c>
       <c r="C217" t="n">
-        <v>0.02412803303793936</v>
+        <v>0.1286426881921604</v>
       </c>
     </row>
     <row r="218">
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>0.0226111389757438</v>
+        <v>0.1205551109927789</v>
       </c>
     </row>
     <row r="220">
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C220" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="221">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C221" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="222">
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.0001512512112341972</v>
+        <v>0.004188586709478851</v>
       </c>
       <c r="C222" t="n">
-        <v>0.0009363413774772192</v>
+        <v>0.004992262389346726</v>
       </c>
     </row>
     <row r="223">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.005425247656134766</v>
+        <v>0.1502409140574178</v>
       </c>
       <c r="C225" t="n">
-        <v>0.03553870011943835</v>
+        <v>0.1894805892809758</v>
       </c>
     </row>
     <row r="226">
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.005425247656134766</v>
+        <v>0.1502409140574178</v>
       </c>
       <c r="C226" t="n">
-        <v>0.03553870011943835</v>
+        <v>0.1894805892809758</v>
       </c>
     </row>
     <row r="227">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.03477092794876928</v>
+        <v>0.9629083000000001</v>
       </c>
       <c r="C227" t="n">
-        <v>0.7286833685908978</v>
+        <v>3.8850986</v>
       </c>
     </row>
     <row r="228">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.004612801312950412</v>
+        <v>0.1277419077522222</v>
       </c>
       <c r="C228" t="n">
-        <v>0.9224063783559301</v>
+        <v>4.917965585123222</v>
       </c>
     </row>
     <row r="229">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.04297888754229857</v>
+        <v>1.190210615035102</v>
       </c>
       <c r="C229" t="n">
-        <v>0.09033066353222184</v>
+        <v>0.481613207537244</v>
       </c>
     </row>
     <row r="230">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.00155723310444006</v>
+        <v>0.04312432166059504</v>
       </c>
       <c r="C231" t="n">
-        <v>0.01013993565708552</v>
+        <v>0.05406278161887105</v>
       </c>
     </row>
     <row r="232">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.002315956513167988</v>
+        <v>0.06413558338892271</v>
       </c>
       <c r="C233" t="n">
-        <v>0.01357388113572822</v>
+        <v>0.07237144261843503</v>
       </c>
     </row>
     <row r="234">
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.002817152647780485</v>
+        <v>0.07801516459128094</v>
       </c>
       <c r="C234" t="n">
-        <v>0.02327481275985413</v>
+        <v>0.1240936</v>
       </c>
     </row>
     <row r="235">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.0008981176057667645</v>
+        <v>0.02487149316932611</v>
       </c>
       <c r="C235" t="n">
-        <v>0.004611874117101123</v>
+        <v>0.02458898672323784</v>
       </c>
     </row>
     <row r="236">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0226111389757438</v>
+        <v>0.1205551109927789</v>
       </c>
     </row>
     <row r="237">
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.0001512512112341972</v>
+        <v>0.004188586709478851</v>
       </c>
       <c r="C237" t="n">
-        <v>0.0009363413774772192</v>
+        <v>0.004992262389346726</v>
       </c>
     </row>
     <row r="238">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1.327260442122343e-06</v>
+        <v>3.67557086156658e-05</v>
       </c>
       <c r="C238" t="n">
-        <v>6.815541795832307e-06</v>
+        <v>3.633821359259762e-05</v>
       </c>
     </row>
     <row r="239">
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.07842821490597864</v>
+        <v>2.171905771350677</v>
       </c>
       <c r="C239" t="n">
-        <v>0.6298148259013326</v>
+        <v>3.357964245980015</v>
       </c>
     </row>
     <row r="240">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.01772534386338556</v>
+        <v>0.490866414366492</v>
       </c>
       <c r="C240" t="n">
-        <v>0.1708940826804124</v>
+        <v>0.9111507</v>
       </c>
     </row>
     <row r="241">
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.06940144259031446</v>
+        <v>1.921928146428794</v>
       </c>
       <c r="C241" t="n">
-        <v>0.1056944428608432</v>
+        <v>0.5635277950428734</v>
       </c>
     </row>
     <row r="242">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.01772534386338556</v>
+        <v>0.490866414366492</v>
       </c>
       <c r="C242" t="n">
-        <v>0.1708940826804124</v>
+        <v>0.9111507</v>
       </c>
     </row>
     <row r="243">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.009026772315664172</v>
+        <v>0.2499776249218826</v>
       </c>
       <c r="C243" t="n">
-        <v>0.5241203830404894</v>
+        <v>2.794436450937141</v>
       </c>
     </row>
     <row r="244">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.002315956513167988</v>
+        <v>0.06413558338892271</v>
       </c>
       <c r="C244" t="n">
-        <v>0.01357388113572822</v>
+        <v>0.07237144261843503</v>
       </c>
     </row>
     <row r="245">
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>2.644412195156787</v>
+        <v>14.09913078858061</v>
       </c>
     </row>
     <row r="246">
@@ -3661,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>2.639872534591853</v>
+        <v>14.07492682062206</v>
       </c>
     </row>
     <row r="247">
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.009489813322629683</v>
+        <v>0.2628005794747314</v>
       </c>
       <c r="C247" t="n">
-        <v>0.05432292409697213</v>
+        <v>0.2896318558294717</v>
       </c>
     </row>
     <row r="248">
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.01823062816214726</v>
+        <v>0.5048592087450079</v>
       </c>
       <c r="C248" t="n">
-        <v>0.1047426964336266</v>
+        <v>0.5584533980258473</v>
       </c>
     </row>
     <row r="249">
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.0006572799257214241</v>
+        <v>0.01820199612828982</v>
       </c>
       <c r="C249" t="n">
-        <v>0.003384643503220513</v>
+        <v>0.01804579918063656</v>
       </c>
     </row>
     <row r="250">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C250" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="251">
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>3.767160488917459e-05</v>
+        <v>0.001043236495602089</v>
       </c>
       <c r="C251" t="n">
-        <v>0.0006800315585437363</v>
+        <v>0.00362570324771248</v>
       </c>
     </row>
     <row r="252">
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C252" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="253">
@@ -3749,10 +3749,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>3.767160488917459e-05</v>
+        <v>0.001043236495602089</v>
       </c>
       <c r="C253" t="n">
-        <v>0.0006800315585437363</v>
+        <v>0.00362570324771248</v>
       </c>
     </row>
     <row r="254">
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C254" t="n">
-        <v>0.0004356984569803854</v>
+        <v>0.002323</v>
       </c>
     </row>
     <row r="255">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.1123573830351156</v>
+        <v>3.111503289477823</v>
       </c>
       <c r="C255" t="n">
-        <v>0.5169707173639261</v>
+        <v>2.756316799374078</v>
       </c>
     </row>
     <row r="256">
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.04872233988309616</v>
+        <v>1.349263543900182</v>
       </c>
       <c r="C256" t="n">
-        <v>0.4870706670780754</v>
+        <v>2.596899625176562</v>
       </c>
     </row>
     <row r="257">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C257" t="n">
         <v>0</v>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.202465493563904</v>
+        <v>5.6068594</v>
       </c>
       <c r="C258" t="n">
-        <v>2.994904965306892</v>
+        <v>15.96784226096333</v>
       </c>
     </row>
     <row r="259">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.1897934749605767</v>
+        <v>5.255934284947665</v>
       </c>
       <c r="C259" t="n">
-        <v>2.825686334061678</v>
+        <v>15.06562451360893</v>
       </c>
     </row>
     <row r="260">
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.0002595140885019131</v>
+        <v>0.007186701204914825</v>
       </c>
       <c r="C260" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.02017481469554738</v>
+        <v>0.5586993982423223</v>
       </c>
       <c r="C261" t="n">
         <v>0</v>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.002565887881492082</v>
+        <v>0.07105691115285848</v>
       </c>
       <c r="C262" t="n">
-        <v>0.01162722743458046</v>
+        <v>0.06199252923162489</v>
       </c>
     </row>
     <row r="263">
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.005331026284536014</v>
+        <v>0.1476316497638822</v>
       </c>
       <c r="C263" t="n">
-        <v>0.02412803303793936</v>
+        <v>0.1286426881921604</v>
       </c>
     </row>
     <row r="264">
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.003190818821613736</v>
+        <v>0.08836306962112112</v>
       </c>
       <c r="C264" t="n">
-        <v>0.01430009427411298</v>
+        <v>0.0762433707683751</v>
       </c>
     </row>
     <row r="265">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="C265" t="n">
-        <v>0.08260576411240525</v>
+        <v>0.4404266</v>
       </c>
     </row>
     <row r="266">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.001026794558510019</v>
+        <v>0.02843493289108863</v>
       </c>
       <c r="C266" t="n">
-        <v>0.01271121062860541</v>
+        <v>0.06777196893212706</v>
       </c>
     </row>
     <row r="267">
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0.003595805982781375</v>
+        <v>0.09957834404394711</v>
       </c>
       <c r="C267" t="n">
-        <v>0.1069442165389368</v>
+        <v>0.5701911747443582</v>
       </c>
     </row>
     <row r="268">
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.003595805982781375</v>
+        <v>0.09957834404394711</v>
       </c>
       <c r="C268" t="n">
-        <v>0.02433845242653155</v>
+        <v>0.1297645747443583</v>
       </c>
     </row>
     <row r="269">
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.003190818821613736</v>
+        <v>0.08836306962112112</v>
       </c>
       <c r="C269" t="n">
-        <v>0.01430009427411298</v>
+        <v>0.0762433707683751</v>
       </c>
     </row>
     <row r="270">
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C270" t="n">
-        <v>0.08260576411240525</v>
+        <v>0.4404266</v>
       </c>
     </row>
     <row r="271">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.00352724889688258</v>
+        <v>0.0976797985943397</v>
       </c>
       <c r="C271" t="n">
-        <v>0.01271163800110132</v>
+        <v>0.06777424754085769</v>
       </c>
     </row>
     <row r="272">
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.0008519035267554192</v>
+        <v>0.02359169067678276</v>
       </c>
       <c r="C272" t="n">
-        <v>0.003855639000818878</v>
+        <v>0.02055699132142089</v>
       </c>
     </row>
     <row r="273">
@@ -4009,10 +4009,10 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.0810443070831566</v>
+        <v>2.244352985721293</v>
       </c>
       <c r="C273" t="n">
-        <v>0.2612973518731839</v>
+        <v>1.393151016894082</v>
       </c>
     </row>
     <row r="274">
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.0291602578042458</v>
+        <v>0.8075324970106788</v>
       </c>
       <c r="C274" t="n">
-        <v>0.5562337505153874</v>
+        <v>2.9656543</v>
       </c>
     </row>
     <row r="275">
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.9626659325679113</v>
+        <v>26.6590244</v>
       </c>
       <c r="C275" t="n">
-        <v>0.7253632075553976</v>
+        <v>3.8673966</v>
       </c>
     </row>
     <row r="276">
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.06403205356449697</v>
+        <v>1.773234120588981</v>
       </c>
       <c r="C276" t="n">
-        <v>0.5595054733682541</v>
+        <v>2.983098043638393</v>
       </c>
     </row>
     <row r="277">
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.9507309874187286</v>
+        <v>26.32851099635644</v>
       </c>
       <c r="C277" t="n">
-        <v>0.2643825402562985</v>
+        <v>1.409600220464013</v>
       </c>
     </row>
     <row r="278">
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1.850474591964506</v>
+        <v>51.24503280922085</v>
       </c>
       <c r="C278" t="n">
-        <v>1.330107066028984</v>
+        <v>7.091690743638393</v>
       </c>
     </row>
     <row r="279">
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.03401773111689054</v>
+        <v>0.9420500852863081</v>
       </c>
       <c r="C279" t="n">
-        <v>0.6349917111396245</v>
+        <v>3.385565685039262</v>
       </c>
     </row>
     <row r="280">
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1.786442538400008</v>
+        <v>49.47179868863186</v>
       </c>
       <c r="C280" t="n">
-        <v>0.7706015926607298</v>
+        <v>4.1085927</v>
       </c>
     </row>
     <row r="281">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0.0148965781711198</v>
+        <v>0.4125296507388089</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0897048560129967</v>
+        <v>0.4782766089244437</v>
       </c>
     </row>
     <row r="282">
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.002502450725078115</v>
+        <v>0.06930015146760052</v>
       </c>
       <c r="C282" t="n">
-        <v>0.01132605285516137</v>
+        <v>0.06038676603283065</v>
       </c>
     </row>
     <row r="283">
@@ -4139,10 +4139,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.008195324917589725</v>
+        <v>0.2269524240472069</v>
       </c>
       <c r="C283" t="n">
-        <v>0.03967613068860557</v>
+        <v>0.21154</v>
       </c>
     </row>
     <row r="284">
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.4052685514460069</v>
+        <v>11.22306693946457</v>
       </c>
       <c r="C284" t="n">
-        <v>14.50562747067511</v>
+        <v>77.33920576150966</v>
       </c>
     </row>
     <row r="285">
@@ -4168,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>1.712811113831438e-08</v>
+        <v>9.13214208975166e-08</v>
       </c>
     </row>
     <row r="286">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0.005425247656134766</v>
+        <v>0.1502409140574178</v>
       </c>
       <c r="C286" t="n">
-        <v>0.03553870011943835</v>
+        <v>0.1894805892809758</v>
       </c>
     </row>
     <row r="287">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0.002817152647780485</v>
+        <v>0.07801516459128094</v>
       </c>
       <c r="C287" t="n">
-        <v>0.02327481275985413</v>
+        <v>0.1240936</v>
       </c>
     </row>
     <row r="288">
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C288" t="n">
-        <v>0.4051767398497886</v>
+        <v>2.160268303895857</v>
       </c>
     </row>
     <row r="289">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.1549577699601656</v>
+        <v>4.291232119659766</v>
       </c>
       <c r="C290" t="n">
         <v>0</v>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.001304471097935263</v>
+        <v>0.03612460527837127</v>
       </c>
       <c r="C291" t="n">
-        <v>0.005903999333521629</v>
+        <v>0.03147817081295786</v>
       </c>
     </row>
     <row r="292">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.002502450725078115</v>
+        <v>0.06930015146760052</v>
       </c>
       <c r="C292" t="n">
-        <v>0.01132605285516137</v>
+        <v>0.06038676603283065</v>
       </c>
     </row>
     <row r="293">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C293" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="294">
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.006164020986813107</v>
+        <v>0.1706997</v>
       </c>
       <c r="C294" t="n">
-        <v>0.1119509467736205</v>
+        <v>0.5968854036286571</v>
       </c>
     </row>
     <row r="295">
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C295" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="296">
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C296" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="297">
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C297" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="298">
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C298" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="299">
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.002817731559248415</v>
+        <v>0.07803119633648647</v>
       </c>
       <c r="C299" t="n">
-        <v>0.01365059838423254</v>
+        <v>0.07278047360172257</v>
       </c>
     </row>
     <row r="300">
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.001284505712135678</v>
+        <v>0.03557170557642924</v>
       </c>
       <c r="C300" t="n">
-        <v>0.005813657151844957</v>
+        <v>0.03099649619448577</v>
       </c>
     </row>
     <row r="301">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.0007186387232242646</v>
+        <v>0.0199012</v>
       </c>
       <c r="C301" t="n">
-        <v>0.08260576411240525</v>
+        <v>0.4404266</v>
       </c>
     </row>
     <row r="302">
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.0007186387232242646</v>
+        <v>0.0199012</v>
       </c>
       <c r="C302" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.01345707707981093</v>
+        <v>0.3726656715340368</v>
       </c>
       <c r="C303" t="n">
-        <v>0.145715296583811</v>
+        <v>0.7769057441932405</v>
       </c>
     </row>
     <row r="304">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.004239524008393639</v>
+        <v>0.1174047716456183</v>
       </c>
       <c r="C304" t="n">
-        <v>0.0191879978339453</v>
+        <v>0.1023040551421131</v>
       </c>
     </row>
     <row r="305">
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.06403205356449697</v>
+        <v>1.773234120588981</v>
       </c>
       <c r="C305" t="n">
-        <v>0.5595054733682541</v>
+        <v>2.983098043638393</v>
       </c>
     </row>
     <row r="306">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.06403205356449697</v>
+        <v>1.773234120588981</v>
       </c>
       <c r="C306" t="n">
-        <v>0.5595054733682541</v>
+        <v>2.983098043638393</v>
       </c>
     </row>
     <row r="307">
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1.777963493994253</v>
+        <v>49.23698924534062</v>
       </c>
       <c r="C307" t="n">
-        <v>0.7322255969928392</v>
+        <v>3.903984589715774</v>
       </c>
     </row>
     <row r="308">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1.686319779856678</v>
+        <v>46.69910779691003</v>
       </c>
       <c r="C308" t="n">
-        <v>1.751527093850979e-08</v>
+        <v>9.338562884098067e-08</v>
       </c>
     </row>
     <row r="309">
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.0112913716649517</v>
+        <v>0.3126909788138585</v>
       </c>
       <c r="C309" t="n">
-        <v>0.4890390515795513</v>
+        <v>2.6073944</v>
       </c>
     </row>
     <row r="310">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C310" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="311">
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>3.767160488917459e-05</v>
+        <v>0.001043236495602089</v>
       </c>
       <c r="C311" t="n">
-        <v>0.0006800315585437363</v>
+        <v>0.00362570324771248</v>
       </c>
     </row>
     <row r="312">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>3.767160488917459e-05</v>
+        <v>0.001043236495602089</v>
       </c>
       <c r="C312" t="n">
-        <v>0.0006800315585437363</v>
+        <v>0.00362570324771248</v>
       </c>
     </row>
     <row r="313">
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C313" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="314">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.01229392802192186</v>
+        <v>0.3404546852863081</v>
       </c>
       <c r="C314" t="n">
-        <v>0.3197882713831903</v>
+        <v>1.70500524507617</v>
       </c>
     </row>
     <row r="315">
@@ -4555,10 +4555,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.02172380309496868</v>
+        <v>0.6015954</v>
       </c>
       <c r="C315" t="n">
-        <v>0.3152034397564344</v>
+        <v>1.680560439963093</v>
       </c>
     </row>
     <row r="316">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="317">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.004372645406780121</v>
+        <v>0.1210912910161342</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0197904482252386</v>
+        <v>0.1055161212776545</v>
       </c>
     </row>
     <row r="318">
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.0008518999157233045</v>
+        <v>0.02359159067678276</v>
       </c>
       <c r="C318" t="n">
-        <v>0.003855639000818878</v>
+        <v>0.02055699132142089</v>
       </c>
     </row>
     <row r="319">
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C319" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="320">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C320" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C321" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>1.588854130498042e-07</v>
+        <v>4.4e-06</v>
       </c>
       <c r="C322" t="n">
         <v>0</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.02717010881089764</v>
+        <v>0.7524194730857763</v>
       </c>
       <c r="C323" t="n">
-        <v>0.2162504259148982</v>
+        <v>1.152975713712302</v>
       </c>
     </row>
     <row r="324">
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.004239524008393639</v>
+        <v>0.1174047716456183</v>
       </c>
       <c r="C324" t="n">
-        <v>0.0191879978339453</v>
+        <v>0.1023040551421131</v>
       </c>
     </row>
     <row r="325">
@@ -4685,10 +4685,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.004239524008393639</v>
+        <v>0.1174047716456183</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0191879978339453</v>
+        <v>0.1023040551421131</v>
       </c>
     </row>
     <row r="326">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.0008519035267554192</v>
+        <v>0.02359169067678276</v>
       </c>
       <c r="C326" t="n">
-        <v>0.003855639000818878</v>
+        <v>0.02055699132142089</v>
       </c>
     </row>
     <row r="327">
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.001292765790419099</v>
+        <v>0.03580045120983524</v>
       </c>
       <c r="C327" t="n">
-        <v>0.006119486463491986</v>
+        <v>0.0326270768852685</v>
       </c>
     </row>
     <row r="328">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.0004695254412967476</v>
+        <v>0.01300252743188016</v>
       </c>
       <c r="C328" t="n">
-        <v>0.003879135459975687</v>
+        <v>0.02068226666666666</v>
       </c>
     </row>
     <row r="329">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.003963520963999851</v>
+        <v>0.1097614432114845</v>
       </c>
       <c r="C329" t="n">
         <v>0</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.004307743236793298</v>
+        <v>0.1192939608367268</v>
       </c>
       <c r="C330" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="C331" t="n">
-        <v>0.2618710352865689</v>
+        <v>1.396209707022409</v>
       </c>
     </row>
     <row r="332">
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.002846614603980864</v>
+        <v>0.07883105199587881</v>
       </c>
       <c r="C332" t="n">
-        <v>0.01430009427411298</v>
+        <v>0.0762433707683751</v>
       </c>
     </row>
     <row r="333">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.0007711698215961697</v>
+        <v>0.02135593916327316</v>
       </c>
       <c r="C333" t="n">
-        <v>0.2475709410124559</v>
+        <v>1.319966336254034</v>
       </c>
     </row>
     <row r="334">
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.008266729626189863</v>
+        <v>0.2289298284659632</v>
       </c>
       <c r="C334" t="n">
-        <v>0.1694881431726233</v>
+        <v>0.9036546957698518</v>
       </c>
     </row>
     <row r="335">
@@ -4815,10 +4815,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>3.611032114768278e-09</v>
+        <v>1e-07</v>
       </c>
       <c r="C335" t="n">
-        <v>1.751527093850979e-08</v>
+        <v>9.338562884098067e-08</v>
       </c>
     </row>
     <row r="336">
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.003826887208812962</v>
+        <v>0.1059776564479138</v>
       </c>
       <c r="C336" t="n">
-        <v>0.01732039437035967</v>
+        <v>0.0923466114642606</v>
       </c>
     </row>
     <row r="337">
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.007533985713860533</v>
+        <v>0.2086380146841755</v>
       </c>
       <c r="C337" t="n">
-        <v>0.0340985731238608</v>
+        <v>0.1818023086785791</v>
       </c>
     </row>
     <row r="338">
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.003826887208812962</v>
+        <v>0.1059776564479138</v>
       </c>
       <c r="C338" t="n">
-        <v>0.01732039437035967</v>
+        <v>0.0923466114642606</v>
       </c>
     </row>
     <row r="339">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.008266726015157749</v>
+        <v>0.2289297284659632</v>
       </c>
       <c r="C339" t="n">
-        <v>0.1694881431726233</v>
+        <v>0.9036546957698518</v>
       </c>
     </row>
     <row r="340">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.00402720200676411</v>
+        <v>0.1115249568203449</v>
       </c>
       <c r="C340" t="n">
-        <v>0.1503001453386781</v>
+        <v>0.8013506406277388</v>
       </c>
     </row>
     <row r="341">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>5.581553752882574e-05</v>
+        <v>0.001545694852741775</v>
       </c>
       <c r="C341" t="n">
-        <v>0.0004356871345867694</v>
+        <v>0.00232293963274382</v>
       </c>
     </row>
     <row r="342">
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.8828827478933554</v>
+        <v>24.449595568053</v>
       </c>
       <c r="C342" t="n">
-        <v>0.5203972956777387</v>
+        <v>2.774586181088563</v>
       </c>
     </row>
     <row r="343">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.00103887781159142</v>
+        <v>0.02876955337347049</v>
       </c>
       <c r="C343" t="n">
-        <v>0.00608707638707989</v>
+        <v>0.03245427708233349</v>
       </c>
     </row>
     <row r="344">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.0002034520820270302</v>
+        <v>0.005634180908969452</v>
       </c>
       <c r="C344" t="n">
-        <v>0.009984551213602973</v>
+        <v>0.05323432318293447</v>
       </c>
     </row>
     <row r="345">
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.0002034520820270302</v>
+        <v>0.005634180908969452</v>
       </c>
       <c r="C345" t="n">
-        <v>0.009984551213602973</v>
+        <v>0.05323432318293447</v>
       </c>
     </row>
     <row r="346">
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.005731418801432847</v>
+        <v>0.1587196851003535</v>
       </c>
       <c r="C346" t="n">
-        <v>0.1099930011283582</v>
+        <v>0.5864462853323326</v>
       </c>
     </row>
     <row r="347">
@@ -4971,10 +4971,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.006164020986813107</v>
+        <v>0.1706997</v>
       </c>
       <c r="C347" t="n">
-        <v>0.1119509467736205</v>
+        <v>0.5968854036286571</v>
       </c>
     </row>
     <row r="348">
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.001304471097935263</v>
+        <v>0.03612460527837127</v>
       </c>
       <c r="C348" t="n">
-        <v>0.005903999333521629</v>
+        <v>0.03147817081295786</v>
       </c>
     </row>
     <row r="349">
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.000199046706942539</v>
+        <v>0.005512183237819582</v>
       </c>
       <c r="C349" t="n">
-        <v>0.001173433281103724</v>
+        <v>0.006256357965772339</v>
       </c>
     </row>
     <row r="350">
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.003190818821613736</v>
+        <v>0.08836306962112112</v>
       </c>
       <c r="C350" t="n">
-        <v>0.01430009427411298</v>
+        <v>0.0762433707683751</v>
       </c>
     </row>
     <row r="351">
@@ -5026,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="C351" t="n">
-        <v>1.436334567364282e-08</v>
+        <v>7.658060630078012e-08</v>
       </c>
     </row>
     <row r="352">
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>3.123542779274561e-06</v>
+        <v>8.65e-05</v>
       </c>
       <c r="C352" t="n">
         <v>0</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.01020948499789219</v>
+        <v>0.282730384926176</v>
       </c>
       <c r="C353" t="n">
-        <v>0.04620777824893978</v>
+        <v>0.2463645834695243</v>
       </c>
     </row>
     <row r="354">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.005331026284536014</v>
+        <v>0.1476316497638822</v>
       </c>
       <c r="C354" t="n">
-        <v>0.02412803303793936</v>
+        <v>0.1286426881921604</v>
       </c>
     </row>
     <row r="355">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.01020948499789219</v>
+        <v>0.282730384926176</v>
       </c>
       <c r="C355" t="n">
-        <v>0.04620777824893978</v>
+        <v>0.2463645834695243</v>
       </c>
     </row>
     <row r="356">
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>2.225279209345545e-05</v>
+        <v>0.0006162446465775457</v>
       </c>
       <c r="C356" t="n">
-        <v>0.0001142690837258693</v>
+        <v>0.0006092449427865303</v>
       </c>
     </row>
   </sheetData>
@@ -12832,7 +12832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C360"/>
+  <dimension ref="A1:C282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12859,10 +12859,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115909.4078740732</v>
+        <v>115909.4078740731</v>
       </c>
       <c r="C2" t="n">
-        <v>561171.130789104</v>
+        <v>561171.1307891065</v>
       </c>
     </row>
     <row r="3">
@@ -12872,4651 +12872,3637 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51281.36901863604</v>
+        <v>51281.36901863628</v>
       </c>
       <c r="C3" t="n">
-        <v>59929.60256938188</v>
+        <v>59320.42377830136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16GS_c_FWD-rt3279</t>
+          <t>2OXOADPt_c_m_FWD-rt2267</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51281.36901863604</v>
+        <v>172355.3704673378</v>
       </c>
       <c r="C4" t="n">
-        <v>59929.60256938188</v>
+        <v>596807.6790439038</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2OXOADPt_c_m_FWD-rt2267</t>
+          <t>3HACD260_rm_FWD-rt2309</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>172355.3704673377</v>
+        <v>632265.5198424255</v>
       </c>
       <c r="C5" t="n">
-        <v>990193.1602236661</v>
+        <v>11720.01008841648</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3HACD260_rm_FWD-rt2309</t>
+          <t>3OACE240_rm_FWD-rt8287</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>632265.5198424241</v>
+        <v>75203.79338508967</v>
       </c>
       <c r="C6" t="n">
-        <v>11720.01008841645</v>
+        <v>17318157.9925003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3OACE240_rm_FWD-rt2975</t>
+          <t>3OACE260_rm_FWD-rt8287</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>583.9069372716421</v>
+        <v>75203.79338508967</v>
       </c>
       <c r="C7" t="n">
-        <v>178647.5225728264</v>
+        <v>17318157.9925003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3OACE240_rm_FWD-rt8287</t>
+          <t>3OACR260_rm_FWD-rt8327</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>583.9069372716421</v>
+        <v>81323.11043386596</v>
       </c>
       <c r="C8" t="n">
-        <v>17318157.99250028</v>
+        <v>8449.497464177499</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3OACE260_rm_FWD-rt2975</t>
+          <t>AASADy_c_FWD-LYS25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75203.79338508948</v>
+        <v>5694336.325804958</v>
       </c>
       <c r="C9" t="n">
-        <v>178647.5225728264</v>
+        <v>24449591.61863667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3OACE260_rm_FWD-rt8287</t>
+          <t>AATA_c_FWD-rt7471</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75203.79338508948</v>
+        <v>61343.54779923162</v>
       </c>
       <c r="C10" t="n">
-        <v>17318157.99250028</v>
+        <v>417154.8823556802</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3OACR260_rm_FWD-rt8327</t>
+          <t>ACACT40ir_c_FWD-rt0310</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81323.11043386596</v>
+        <v>10196.43255604256</v>
       </c>
       <c r="C11" t="n">
-        <v>8449.497464177484</v>
+        <v>7704.033838260354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AASADy_c_FWD-LYS25</t>
+          <t>ACCOAC_c_FWD-rt0271</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5694336.325804932</v>
+        <v>30376.55608344751</v>
       </c>
       <c r="C12" t="n">
-        <v>24430302.66677857</v>
+        <v>146775.3646711609</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AATA_c_FWD-rt0172</t>
+          <t>ACGAM6PS_c_FWD-rt4107</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20503.2113864469</v>
+        <v>9401.574433323953</v>
       </c>
       <c r="C13" t="n">
-        <v>53334.00600774083</v>
+        <v>10323.60269823155</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AATA_c_FWD-rt4039</t>
+          <t>ACGAMPM_c_FWD-rt4597</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20503.2113864469</v>
+        <v>3117.390709153988</v>
       </c>
       <c r="C14" t="n">
-        <v>22307.16150792285</v>
+        <v>3083.565494108327</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AATA_c_FWD-rt7471</t>
+          <t>ACGK_m_FWD-rt1009</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20503.2113864469</v>
+        <v>125888.0212749795</v>
       </c>
       <c r="C15" t="n">
-        <v>417809.4145928964</v>
+        <v>37527.15658120445</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ABTA_c_FWD-rt2569</t>
+          <t>ACHBS_m_FWD-rt7317</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>342694.7194840358</v>
+        <v>29737.46700603436</v>
       </c>
       <c r="C16" t="n">
-        <v>537.7381857168912</v>
+        <v>12689709356913.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ABTA_c_FWD-rt7537</t>
+          <t>ACLS_m_FWD-rt7317</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>342694.7194840358</v>
+        <v>29737.46700603436</v>
       </c>
       <c r="C17" t="n">
-        <v>537.7381857168912</v>
+        <v>12689709356913.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ACACT40ir_c_FWD-rt0310</t>
+          <t>ACOADS180_rm_FWD-rt1362</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10196.43255604253</v>
+        <v>2229.344095069182</v>
       </c>
       <c r="C18" t="n">
-        <v>7704.033804864287</v>
+        <v>30777.29013325594</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ACCOAC_c_FWD-rt0271</t>
+          <t>ACONTa_m_FWD-rt6232</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30376.55608344749</v>
+        <v>90114.14441583032</v>
       </c>
       <c r="C19" t="n">
-        <v>146775.3646711608</v>
+        <v>2484720.773038713</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACGAM6PS_c_FWD-rt4107</t>
+          <t>ACONTb_m_FWD-rt6232</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9401.574433323924</v>
+        <v>90114.14441583032</v>
       </c>
       <c r="C20" t="n">
-        <v>10323.60269823155</v>
+        <v>2484720.773038713</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACGAMPM_c_FWD-rt4597</t>
+          <t>ACOTAi_m_FWD-rt6510</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3117.390709153986</v>
+        <v>176964.7269908072</v>
       </c>
       <c r="C21" t="n">
-        <v>3083.565494108325</v>
+        <v>72031.24354890303</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACGK_m_FWD-rt1009</t>
+          <t>ACS_c_FWD-rt6229_c</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>125888.0212749794</v>
+        <v>62987.20735925796</v>
       </c>
       <c r="C22" t="n">
-        <v>59538.34883427624</v>
+        <v>13562.47385182745</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ACHBS_m_FWD-ILV26</t>
+          <t>ADK1_c_FWD-rt3932</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29737.46700603432</v>
+        <v>127018.1102646465</v>
       </c>
       <c r="C23" t="n">
-        <v>39147.23702982564</v>
+        <v>137362.8184974645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ACHBS_m_FWD-rt7317</t>
+          <t>ADNK1_c_FWD-rt0017</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29737.46700603432</v>
+        <v>1623.174552441999</v>
       </c>
       <c r="C24" t="n">
-        <v>12707943826999.64</v>
+        <v>4384.145233736586</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ACLS_m_FWD-ILV26</t>
+          <t>ADPATPt_c_m_FWD-rt4336</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29737.46700603432</v>
+        <v>964725.6648004968</v>
       </c>
       <c r="C25" t="n">
-        <v>39147.23702982564</v>
+        <v>674258.7316406402</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ACLS_m_FWD-rt7317</t>
+          <t>ADSK_c_FWD-rt0341</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29737.46700603432</v>
+        <v>6844.173703402113</v>
       </c>
       <c r="C26" t="n">
-        <v>12707943826999.64</v>
+        <v>9556.319040025741</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ACOADS180_rm_FWD-rt1362</t>
+          <t>ADSL1r_c_FWD-rt7437</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2229.344095069181</v>
+        <v>40962.97900593253</v>
       </c>
       <c r="C27" t="n">
-        <v>30777.29013325593</v>
+        <v>77359.41393935283</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ACONTa_m_FWD-rt3256</t>
+          <t>ADSL2i_c_FWD-rt7437</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90114.14441583</v>
+        <v>40962.97900593253</v>
       </c>
       <c r="C28" t="n">
-        <v>236508.8303380169</v>
+        <v>77359.41393935283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ACONTa_m_FWD-rt6232</t>
+          <t>ADSS_c_FWD-rt3802</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>90114.14441583</v>
+        <v>12902.18823620558</v>
       </c>
       <c r="C29" t="n">
-        <v>2035976.004420073</v>
+        <v>13153.54561527693</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ACONTb_m_FWD-rt3256</t>
+          <t>AFAT_c_FWD-rt3174_c</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>90114.14441583</v>
+        <v>130.9489782089105</v>
       </c>
       <c r="C30" t="n">
-        <v>236508.8303380169</v>
+        <v>55.23192228813407</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ACONTb_m_FWD-rt6232</t>
+          <t>AGPAT_rm_FWD-rt2059_rm</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>90114.14441583</v>
+        <v>144966.5436492761</v>
       </c>
       <c r="C31" t="n">
-        <v>2035976.004420073</v>
+        <v>43047.38786693202</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ACOTAi_m_FWD-rt6510</t>
+          <t>AGPRi_m_FWD-rt1009</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>176964.726990807</v>
+        <v>125888.0212749795</v>
       </c>
       <c r="C32" t="n">
-        <v>230869.647857948</v>
+        <v>37527.15658120445</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ACS_c_FWD-rt6229_c</t>
+          <t>AHCi_c_FWD-rt4544</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>62987.20735925772</v>
+        <v>820.2500538072118</v>
       </c>
       <c r="C33" t="n">
-        <v>4706.835754380768</v>
+        <v>3722.278823065313</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ADK1_c_FWD-rt3932</t>
+          <t>AHSERL2_c_FWD-rt8250</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>127018.1102646463</v>
+        <v>3406.612663408078</v>
       </c>
       <c r="C34" t="n">
-        <v>137040.4038184801</v>
+        <v>507307.9583782745</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ADK1_c_FWD-rt7128_c</t>
+          <t>AICART_c_FWD-rt4053</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>127018.1102646463</v>
+        <v>115517.9447339925</v>
       </c>
       <c r="C35" t="n">
-        <v>137040.4038184801</v>
+        <v>11862.19442861235</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ADNK1_c_FWD-rt0017</t>
+          <t>AIRC1_c_FWD-rt3764</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1623.174552441997</v>
+        <v>7455.520003341832</v>
       </c>
       <c r="C36" t="n">
-        <v>4384.375973099568</v>
+        <v>18852.70133016234</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ADPATPt_c_m_FWD-rt4336</t>
+          <t>AKGCITta_m_FWD-rt8378</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>964725.6648004956</v>
+        <v>0.0540066385673337</v>
       </c>
       <c r="C37" t="n">
-        <v>665149.8504395016</v>
+        <v>22317.86047726016</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ADSK_c_FWD-rt0341</t>
+          <t>AKGDH_m_FWD-KGDCPLX2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6844.173703402104</v>
+        <v>327265.9186139996</v>
       </c>
       <c r="C38" t="n">
-        <v>9562.677366872915</v>
+        <v>701809.3667236899</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ADSL1r_c_FWD-rt7437</t>
+          <t>AKGMALta_m_FWD-rt2267</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40962.97900593252</v>
+        <v>172355.3704673378</v>
       </c>
       <c r="C39" t="n">
-        <v>77340.83055883308</v>
+        <v>596807.6790439038</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ADSL2i_c_FWD-rt7437</t>
+          <t>ALAS_m_FWD-rt0309</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>40962.97900593252</v>
+        <v>181.7131391711197</v>
       </c>
       <c r="C40" t="n">
-        <v>77340.83055883308</v>
+        <v>131.1170561772125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ADSS_c_FWD-rt3802</t>
+          <t>ALATRS_c_FWD-rt3605</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>12902.18823620557</v>
+        <v>17029.16630847623</v>
       </c>
       <c r="C41" t="n">
-        <v>13142.11074072365</v>
+        <v>38803.44535385368</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AFAT_c_FWD-rt3174_c</t>
+          <t>ANPRT_c_FWD-rt1532</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>130.9489782089105</v>
+        <v>130607.1698005911</v>
       </c>
       <c r="C42" t="n">
-        <v>77.30925817288464</v>
+        <v>50006.98131196326</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AGPAT_rm_FWD-rt2059_rm</t>
+          <t>ANS_c_FWD-TRP23</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>144966.543649276</v>
+        <v>90711.91737234942</v>
       </c>
       <c r="C43" t="n">
-        <v>43086.44154114432</v>
+        <v>22612.54327617105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AGPAT_rm_FWD-rt7662</t>
+          <t>ARGSL_c_FWD-rt3236</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>144966.543649276</v>
+        <v>45680.68369569929</v>
       </c>
       <c r="C44" t="n">
-        <v>43086.44154114432</v>
+        <v>9512.494250015272</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AGPRi_m_FWD-rt1009</t>
+          <t>ARGSS_c_FWD-rt7828</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>125888.0212749794</v>
+        <v>35874.59457915842</v>
       </c>
       <c r="C45" t="n">
-        <v>59538.34883427624</v>
+        <v>6352.473530635003</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AHCi_c_FWD-rt4544</t>
+          <t>ARGTRS_c_FWD-rt1711</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>820.2500538072084</v>
+        <v>13817.24567626451</v>
       </c>
       <c r="C46" t="n">
-        <v>3722.474728127448</v>
+        <v>14089.8073435816</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AHSERL2_c_FWD-rt8250</t>
+          <t>ASAD_c_FWD-rt1962</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3406.612663408079</v>
+        <v>52200.70470673025</v>
       </c>
       <c r="C47" t="n">
-        <v>660242.1723479712</v>
+        <v>16945.53653206875</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AICART_c_FWD-rt4053</t>
+          <t>ASNS1_c_FWD-rt6769</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>115517.9447339926</v>
+        <v>46128.98870718089</v>
       </c>
       <c r="C48" t="n">
-        <v>11857.01098512841</v>
+        <v>3692.33058563159</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AIRC1_c_FWD-rt3764</t>
+          <t>ASNTRS_c_FWD-rt0799</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7455.520003341817</v>
+        <v>6209.615102163374</v>
       </c>
       <c r="C49" t="n">
-        <v>19049.30761013132</v>
+        <v>12227.24949277424</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AKGCITta_m_FWD-rt8378</t>
+          <t>ASPCT_c_FWD-rt8313</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0540066385673334</v>
+        <v>13004.23377875781</v>
       </c>
       <c r="C50" t="n">
-        <v>22482.5659771631</v>
+        <v>2564946472007.423</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AKGDH_m_FWD-KGDCPLX</t>
+          <t>ASPK_c_FWD-rt6294</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>327265.9186139996</v>
+        <v>108480.3930827836</v>
       </c>
       <c r="C51" t="n">
-        <v>545291.1629430047</v>
+        <v>44230.93676567762</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AKGDH_m_FWD-KGDCPLX2</t>
+          <t>ASPTRS_c_FWD-rt5890</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>327265.9186139996</v>
+        <v>25975.78424951706</v>
       </c>
       <c r="C52" t="n">
-        <v>545291.1629430047</v>
+        <v>10694.76237343283</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AKGMALta_m_FWD-rt2267</t>
+          <t>ATPASEP2e_c_FWD-rt0602_c</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>172355.3704673377</v>
+        <v>65219.84215832839</v>
       </c>
       <c r="C53" t="n">
-        <v>990193.1602236661</v>
+        <v>102923.0212967069</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ALAS_m_FWD-rt0309</t>
+          <t>ATPPRT_c_FWD-rt1520</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>181.7131391711194</v>
+        <v>3341.017399637837</v>
       </c>
       <c r="C54" t="n">
-        <v>183.0219387856733</v>
+        <v>3502.295638251149</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ALATRS_c_FWD-rt3605</t>
+          <t>ATPS_m_FWD-ATPSCPLX</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>17029.16630847623</v>
+        <v>35984.09696387159</v>
       </c>
       <c r="C55" t="n">
-        <v>38734.4588142096</v>
+        <v>3375700.396809226</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMETt_c_m_REV-rt3664</t>
+          <t>BPNT_c_FWD-rt2305</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.494639137106276e-09</v>
+        <v>12376.56005482157</v>
       </c>
       <c r="C56" t="n">
-        <v>7.703033031664811e-12</v>
+        <v>6561.090821950577</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ANPRT_c_FWD-rt1532</t>
+          <t>C22STDSy_c_FWD-rt3348</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>130607.1698005908</v>
+        <v>9934.405811783592</v>
       </c>
       <c r="C57" t="n">
-        <v>555794.3905871472</v>
+        <v>10904.2562416876</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ANS_c_FWD-TRP23</t>
+          <t>C24STR_r_FWD-rt2613</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>90711.91737234936</v>
+        <v>12063.06600273226</v>
       </c>
       <c r="C58" t="n">
-        <v>22588.10907540894</v>
+        <v>5050.358805186208</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ARGSL_c_FWD-rt3236</t>
+          <t>C5STDS_c_FWD-rt0413</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>45680.68369569924</v>
+        <v>9746.176246735782</v>
       </c>
       <c r="C59" t="n">
-        <v>9498.286782662437</v>
+        <v>27750.0741331697</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ARGSS_c_FWD-rt7828</t>
+          <t>C8STI_c_FWD-rt1745</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>35874.59457915839</v>
+        <v>4285.257172962481</v>
       </c>
       <c r="C60" t="n">
-        <v>6342.985739323476</v>
+        <v>12342.04469808808</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ARGTRS_c_FWD-rt1711</t>
+          <t>CBPS_c_FWD-rt3934</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>13817.2456762645</v>
+        <v>13004.23377875781</v>
       </c>
       <c r="C61" t="n">
-        <v>14068.76339100931</v>
+        <v>12053.44831897393</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ASAD_c_FWD-rt1962</t>
+          <t>CDPDAGS_rm_FWD-rt4513_rm</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52200.7047067302</v>
+        <v>24669.86417185151</v>
       </c>
       <c r="C62" t="n">
-        <v>16943.53214264325</v>
+        <v>33088.64952944367</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ASNS1_c_FWD-rt6769</t>
+          <t>CHORM_c_FWD-rt1336</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>46128.98870718084</v>
+        <v>121075.0424481346</v>
       </c>
       <c r="C63" t="n">
-        <v>3691.358356222188</v>
+        <v>36690.2000573343</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASNTRS_c_FWD-rt0799</t>
+          <t>CHORS_c_FWD-rt5669</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6209.615102163372</v>
+        <v>58940.02773099929</v>
       </c>
       <c r="C64" t="n">
-        <v>12347.50497940159</v>
+        <v>19666.11375412281</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ASPCT_c_FWD-rt8313</t>
+          <t>CHTNS_c_FWD-rt0073</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>13004.23377875778</v>
+        <v>21272.83334627666</v>
       </c>
       <c r="C65" t="n">
-        <v>2564964779923.876</v>
+        <v>2864.406983447756</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ASPK_c_FWD-rt6294</t>
+          <t>CITMALta_m_FWD-rt2146</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>108480.3930827834</v>
+        <v>669586.9713602242</v>
       </c>
       <c r="C66" t="n">
-        <v>44672.42923656804</v>
+        <v>798591.776619886</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ASPTA_c_FWD-rt0568_c</t>
+          <t>CPPPGO_c_FWD-rt5829</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>120067.7802272165</v>
+        <v>25.69977404039327</v>
       </c>
       <c r="C67" t="n">
-        <v>1324569.579576451</v>
+        <v>21.09752273900273</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ASPTRS_c_FWD-rt5890</t>
+          <t>CS_m_FWD-CIT13</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>25975.78424951702</v>
+        <v>218910.9213977888</v>
       </c>
       <c r="C68" t="n">
-        <v>10678.05261298753</v>
+        <v>54616.44692014272</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ATPASEP2e_c_FWD-rt0602_c</t>
+          <t>CTPS2_c_FWD-rt8107</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>65219.84215832809</v>
+        <v>12066.04264763867</v>
       </c>
       <c r="C69" t="n">
-        <v>44294.70139072092</v>
+        <v>9827.476961786177</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ATPASEP2e_c_FWD-rt5249</t>
+          <t>CYSS_c_FWD-rt3663</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>65219.84215832809</v>
+        <v>3406.612663408078</v>
       </c>
       <c r="C70" t="n">
-        <v>44294.70139072092</v>
+        <v>1409.552229189059</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ATPPRT_c_FWD-rt1520</t>
+          <t>CYSTGL_c_FWD-rt1131</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3341.017399637833</v>
+        <v>13858.71111582983</v>
       </c>
       <c r="C71" t="n">
-        <v>3529.861051534985</v>
+        <v>12400.30122826649</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BPNT_c_FWD-rt2305</t>
+          <t>CYSTRS_c_FWD-rt1487</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>12376.56005482154</v>
+        <v>9704.639446341233</v>
       </c>
       <c r="C72" t="n">
-        <v>6631.774004351664</v>
+        <v>8848.981244591925</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C22STDSy_c_FWD-rt3348</t>
+          <t>CYSTS_c_FWD-rt7344</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9934.405811783568</v>
+        <v>18568.45228640064</v>
       </c>
       <c r="C73" t="n">
-        <v>10904.25624168758</v>
+        <v>13127.32981224449</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C24STR_r_FWD-rt2613</t>
+          <t>DDPA_c_FWD-rt2234_c</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>12063.06600273223</v>
+        <v>11002.7089090439</v>
       </c>
       <c r="C74" t="n">
-        <v>5101.372530491112</v>
+        <v>8215.301335056265</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C5STDS_c_FWD-rt0413</t>
+          <t>DGAT_rm_FWD-rt8092_rm</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9746.176246735751</v>
+        <v>9130.336498101964</v>
       </c>
       <c r="C75" t="n">
-        <v>27750.07413316969</v>
+        <v>147662231754.6685</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C8STI_c_FWD-rt1745</t>
+          <t>DHAD1_m_FWD-rt1321</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4285.25717296248</v>
+        <v>35360.01405234144</v>
       </c>
       <c r="C76" t="n">
-        <v>12342.04469808808</v>
+        <v>41268.49041888629</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CBPS_c_FWD-CPA12</t>
+          <t>DHAD2_m_FWD-rt1321</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5512.011469324596</v>
+        <v>35360.01405234144</v>
       </c>
       <c r="C77" t="n">
-        <v>12043.08727967876</v>
+        <v>41268.49041888629</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CBPS_c_FWD-rt3934</t>
+          <t>DHFRi_c_FWD-rt3791_c</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5512.011469324596</v>
+        <v>4004.75933493307</v>
       </c>
       <c r="C78" t="n">
-        <v>12043.08727967876</v>
+        <v>635.7782586689142</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CDPDAGS_rm_FWD-rt4513_rm</t>
+          <t>DHORDfum_c_FWD-rt6498</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>24669.86417185151</v>
+        <v>24522.81852444569</v>
       </c>
       <c r="C79" t="n">
-        <v>33088.64952944365</v>
+        <v>24014.47346466032</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CHORM_c_FWD-rt1336</t>
+          <t>DHORTS_c_REV-rt3923</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>121075.0424481345</v>
+        <v>14983.54330225835</v>
       </c>
       <c r="C80" t="n">
-        <v>36974.28683676528</v>
+        <v>29082.80682186364</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHORS_c_FWD-rt5669</t>
+          <t>DHQS_c_FWD-rt5884</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>58940.02773099901</v>
+        <v>265929.8632596141</v>
       </c>
       <c r="C81" t="n">
-        <v>19930.78276410687</v>
+        <v>291580.9706850972</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt0073</t>
+          <t>DHQTi_c_FWD-rt5884</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>21272.83334627663</v>
+        <v>265929.8632596141</v>
       </c>
       <c r="C82" t="n">
-        <v>2864.406983447754</v>
+        <v>291580.9706850972</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt0144</t>
+          <t>DMATT_c_FWD-rt4576</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>21272.83334627663</v>
+        <v>5319.136842925139</v>
       </c>
       <c r="C83" t="n">
-        <v>2864.406983447754</v>
+        <v>18294.13970563402</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt0540</t>
+          <t>DOLPMMT_r_FWD-PMT12</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>21272.83334627663</v>
+        <v>160143.4252464789</v>
       </c>
       <c r="C84" t="n">
-        <v>2864.406983447754</v>
+        <v>253892.4401577618</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt1343</t>
+          <t>DOLPMT_c_FWD-rt5116</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21272.83334627663</v>
+        <v>18763.25883723437</v>
       </c>
       <c r="C85" t="n">
-        <v>2864.406983447754</v>
+        <v>519914.5935770405</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt1388</t>
+          <t>DPMVD_c_FWD-rt3542</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>21272.83334627663</v>
+        <v>15690.08535490663</v>
       </c>
       <c r="C86" t="n">
-        <v>2864.406983447754</v>
+        <v>36238.62816453257</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt6173</t>
+          <t>DTMPK_c_FWD-rt6884</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>21272.83334627663</v>
+        <v>6577.992056542359</v>
       </c>
       <c r="C87" t="n">
-        <v>2864.406983447754</v>
+        <v>2892.524838725803</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt6592</t>
+          <t>DUTPDP_c_FWD-rt5532</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>21272.83334627663</v>
+        <v>741.9963280351102</v>
       </c>
       <c r="C88" t="n">
-        <v>2864.406983447754</v>
+        <v>622.4043717649732</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHTNS_c_FWD-rt7460</t>
+          <t>ECOAH100_x_FWD-rt8147</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>21272.83334627663</v>
+        <v>8558443.340694841</v>
       </c>
       <c r="C89" t="n">
-        <v>2864.406983447754</v>
+        <v>0.1325315505948488</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CITMALta_m_FWD-rt2146</t>
+          <t>ECOAR260_rm_FWD-rt7873</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>669586.971360222</v>
+        <v>262690.109439384</v>
       </c>
       <c r="C90" t="n">
-        <v>876882.6216178417</v>
+        <v>11711.64163853789</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CRNOAT_c_FWD-rt5212_c</t>
+          <t>ENO_c_FWD-rt0669</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>18568.45228640065</v>
+        <v>496701.1052072574</v>
       </c>
       <c r="C91" t="n">
-        <v>49777.6778631018</v>
+        <v>104673.8475384344</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CRNOAT_m_FWD-rt0947</t>
+          <t>FBA_c_FWD-rt7052</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3302299.126268654</v>
+        <v>401434.6700222904</v>
       </c>
       <c r="C92" t="n">
-        <v>21992.31603141419</v>
+        <v>91350.28482654002</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CRNOAT_m_FWD-rt5877_m</t>
+          <t>FCLT_m_FWD-rt7907</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3302299.126268654</v>
+        <v>8.820442001467093</v>
       </c>
       <c r="C93" t="n">
-        <v>21992.31603141419</v>
+        <v>17.81859782622487</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CS_m_FWD-CIT13</t>
+          <t>FDH_c_FWD-rt3584</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>218910.9213977886</v>
+        <v>385395324.3915855</v>
       </c>
       <c r="C94" t="n">
-        <v>52587.76691318436</v>
+        <v>70917624981111.31</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CS_m_FWD-rt2960</t>
+          <t>FE2t_c_e_FWD-rt0996</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>218910.9213977886</v>
+        <v>339.565993936351</v>
       </c>
       <c r="C95" t="n">
-        <v>52587.76691318436</v>
+        <v>54.31449446929678</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CS_m_FWD-rt2963</t>
+          <t>FTHFL_m_REV-rt6998</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>218910.9213977886</v>
+        <v>1922045.616244709</v>
       </c>
       <c r="C96" t="n">
-        <v>52587.76691318436</v>
+        <v>134784.2998981823</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CTPS2_c_FWD-rt8107</t>
+          <t>FUM_c_FWD-rt5633_c</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>12066.04264763865</v>
+        <v>234177.081377818</v>
       </c>
       <c r="C97" t="n">
-        <v>9882.687620211876</v>
+        <v>18956.9196572943</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CYSS_c_FWD-rt3663</t>
+          <t>FUM_m_FWD-rt5633_m</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3406.612663408079</v>
+        <v>556873.0489804083</v>
       </c>
       <c r="C98" t="n">
-        <v>8.1065336197194</v>
+        <v>82949152314501.05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CYSTGL_c_FWD-rt1131</t>
+          <t>G3PAT_rm_FWD-rt7067</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>13858.7111158298</v>
+        <v>18568.45228640065</v>
       </c>
       <c r="C99" t="n">
-        <v>45837.00358924896</v>
+        <v>61400.81297047168</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CYSTRS_c_FWD-rt1487</t>
+          <t>G3PD1r_c_FWD-rt3786_c</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>9704.639446341227</v>
+        <v>708616.7237750657</v>
       </c>
       <c r="C100" t="n">
-        <v>8833.883410075032</v>
+        <v>3983.890380098625</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CYSTS_c_FWD-rt7344</t>
+          <t>G5SDy_c_FWD-rt7905</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>18568.45228640065</v>
+        <v>54049.6002045817</v>
       </c>
       <c r="C101" t="n">
-        <v>265851.4684025254</v>
+        <v>0.3775602134956715</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DDPA_c_FWD-rt2234_c</t>
+          <t>G6PDH2i_c_FWD-rt1632</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>11002.70890904389</v>
+        <v>118557.5380167461</v>
       </c>
       <c r="C102" t="n">
-        <v>11729.60284452289</v>
+        <v>238200.6348598707</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DDPA_c_FWD-rt3787_c</t>
+          <t>GALUi_c_FWD-rt3384</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>11002.70890904389</v>
+        <v>846433.6170102336</v>
       </c>
       <c r="C103" t="n">
-        <v>11729.60284452289</v>
+        <v>37018.26683502633</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DGAT_rm_FWD-rt8092_rm</t>
+          <t>GAPD_c_FWD-rt2245</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>9130.33649810196</v>
+        <v>716723.3803490434</v>
       </c>
       <c r="C104" t="n">
-        <v>147662231754.6684</v>
+        <v>329186.2207189633</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DHAD1_m_FWD-rt1321</t>
+          <t>GARFT_c_FWD-rt5227</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>35360.01405234141</v>
+        <v>18606.44391043915</v>
       </c>
       <c r="C105" t="n">
-        <v>41327.7911509104</v>
+        <v>38558.76410626638</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DHAD2_m_FWD-rt1321</t>
+          <t>GF6PTA_c_FWD-rt3731</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>35360.01405234141</v>
+        <v>2699.558006705077</v>
       </c>
       <c r="C106" t="n">
-        <v>41327.7911509104</v>
+        <v>227728895809.7878</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DHFRi_c_FWD-rt3791_c</t>
+          <t>GHMT2r_c_FWD-rt1299</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4004.759334933036</v>
+        <v>132765.4032245437</v>
       </c>
       <c r="C107" t="n">
-        <v>635.77825867134</v>
+        <v>116095.8069685782</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DHORDfum_c_FWD-rt6498</t>
+          <t>GK1_c_FWD-rt3157</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>24522.81852444567</v>
+        <v>4036.91793697842</v>
       </c>
       <c r="C108" t="n">
-        <v>24014.64487368528</v>
+        <v>4575.088882528555</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DHORTS_c_REV-rt3923</t>
+          <t>GLCt_c_e_FWD-rt4674</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>14983.54330225835</v>
+        <v>5611787.457547272</v>
       </c>
       <c r="C109" t="n">
-        <v>29083.01440732531</v>
+        <v>20706067.7852834</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DHQS_c_FWD-rt3937</t>
+          <t>GLNS_c_FWD-rt3476</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>265929.863259614</v>
+        <v>1103315.835534354</v>
       </c>
       <c r="C110" t="n">
-        <v>56822.73492430584</v>
+        <v>284564.8830100736</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DHQS_c_FWD-rt5884</t>
+          <t>GLNTRS_c_FWD-rt5012</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>265929.863259614</v>
+        <v>17315.47474321497</v>
       </c>
       <c r="C111" t="n">
-        <v>292550.0526924005</v>
+        <v>19027.0712716678</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DHQTi_c_FWD-rt2204</t>
+          <t>GLU5K_c_FWD-rt6820</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>265929.863259614</v>
+        <v>205857.5251750048</v>
       </c>
       <c r="C112" t="n">
-        <v>58306.10780104272</v>
+        <v>4.411967762389052</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DHQTi_c_FWD-rt5884</t>
+          <t>GLUDy_c_FWD-rt3880</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>265929.863259614</v>
+        <v>112672.3890786229</v>
       </c>
       <c r="C113" t="n">
-        <v>292550.0526924005</v>
+        <v>696117.8629595879</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DMATT_c_FWD-rt4576</t>
+          <t>GLUPRT_c_FWD-rt6932</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5319.136842925104</v>
+        <v>10189.93477578383</v>
       </c>
       <c r="C114" t="n">
-        <v>18294.1396263311</v>
+        <v>23054.05820032469</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DOLPMMT_r_FWD-PMT12</t>
+          <t>GLUTRS_c_FWD-rt2385</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>160143.4252464786</v>
+        <v>29478.84880083638</v>
       </c>
       <c r="C115" t="n">
-        <v>253892.4401577618</v>
+        <v>22472.05061588834</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DOLPMMT_r_FWD-rt3753</t>
+          <t>GLUt_c_m_FWD-rt4150</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>160143.4252464786</v>
+        <v>1018791.95153693</v>
       </c>
       <c r="C116" t="n">
-        <v>253892.4401577618</v>
+        <v>1566008.667156989</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DOLPMT_c_FWD-rt5116</t>
+          <t>GLYCL_m_FWD-GCV123LPD1</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>18763.25883723436</v>
+        <v>244947.9411074352</v>
       </c>
       <c r="C117" t="n">
-        <v>519914.5935770376</v>
+        <v>621911.5763438568</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DPMVD_c_FWD-rt3542</t>
+          <t>GLYGS_c_FWD-rt12285634</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>15690.0853549066</v>
+        <v>1071109.175293076</v>
       </c>
       <c r="C118" t="n">
-        <v>36238.62800744244</v>
+        <v>234143.4419839105</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DTMPK_c_FWD-rt6884</t>
+          <t>GLYTRS_c_FWD-rt7136</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>6577.992056542355</v>
+        <v>22748.03085129845</v>
       </c>
       <c r="C119" t="n">
-        <v>2892.524838725801</v>
+        <v>17941.15485285971</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DUTPDP_c_FWD-rt0031</t>
+          <t>GLYt_c_m_FWD-rt4150</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>228.5271871007249</v>
+        <v>709928.0773123157</v>
       </c>
       <c r="C120" t="n">
-        <v>673.2716899726296</v>
+        <v>1566008.667156989</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DUTPDP_c_FWD-rt5532</t>
+          <t>GND_c_FWD-rt2224</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>228.5271871007249</v>
+        <v>32686.12794731501</v>
       </c>
       <c r="C121" t="n">
-        <v>673.2716899726296</v>
+        <v>135550.114375045</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ECOAR260_rm_FWD-rt7873</t>
+          <t>GRTT_c_FWD-rt4576</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>262690.1094393838</v>
+        <v>5319.136842925139</v>
       </c>
       <c r="C122" t="n">
-        <v>11711.64163853786</v>
+        <v>18294.13970563402</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ENO_c_FWD-rt0669</t>
+          <t>HACD100i_x_FWD-rt2994</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>496701.1052072568</v>
+        <v>8558443.340694841</v>
       </c>
       <c r="C123" t="n">
-        <v>88803.48419393365</v>
+        <v>0.0389804161586853</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA_c_FWD-rt7052</t>
+          <t>HACNH_m_FWD-rt6232</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>401434.6700222892</v>
+        <v>9601.307604007616</v>
       </c>
       <c r="C124" t="n">
-        <v>81670.25423649311</v>
+        <v>2484720.773038713</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FDH_c_FWD-rt3584</t>
+          <t>HCITR_m_FWD-rt7648</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>385395324.391584</v>
+        <v>41659.54469771365</v>
       </c>
       <c r="C125" t="n">
-        <v>150121717000195.3</v>
+        <v>48394.29601024477</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FE2t_c_e_FWD-rt0996</t>
+          <t>HCITS_m_FWD-rt6488_m</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>339.565992778319</v>
+        <v>7502.871322486304</v>
       </c>
       <c r="C126" t="n">
-        <v>54.57135112156548</v>
+        <v>3899547576839.245</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FKYNH_c_FWD-rt0172</t>
+          <t>HCO3E_c_FWD-rt4213</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>473448.4776726156</v>
+        <v>622936.8010802411</v>
       </c>
       <c r="C127" t="n">
-        <v>53334.00600774083</v>
+        <v>307341.0942279598</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FKYNH_c_FWD-rt3408</t>
+          <t>HEMEOS_m_FWD-rt2735</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>473448.4776726156</v>
+        <v>966396.1497556216</v>
       </c>
       <c r="C128" t="n">
-        <v>3351.414209410235</v>
+        <v>37095.08928294634</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FKYNH_c_FWD-rt6420</t>
+          <t>HEX1_c_FWD-rt1896</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>473448.4776726156</v>
+        <v>1266756.205724464</v>
       </c>
       <c r="C129" t="n">
-        <v>3351.414209410235</v>
+        <v>373468.7308706307</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FTHFL_m_REV-rt6998</t>
+          <t>HICITD_m_FWD-rt2060</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1922045.616244706</v>
+        <v>6590.732743703385</v>
       </c>
       <c r="C130" t="n">
-        <v>180540.2352900261</v>
+        <v>5429.886252954555</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FUM_c_FWD-rt5633_c</t>
+          <t>HISTD_c_FWD-rt3278</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>234177.081377818</v>
+        <v>5784.712267411606</v>
       </c>
       <c r="C131" t="n">
-        <v>8714566647219.348</v>
+        <v>37095.08928294634</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FUM_m_FWD-rt5633_m</t>
+          <t>HISTP_c_FWD-rt1838</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>556873.0489804067</v>
+        <v>77451.78284265308</v>
       </c>
       <c r="C132" t="n">
-        <v>136900.6975963469</v>
+        <v>115484.6912942312</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>G3PAT_rm_FWD-rt2297_rm</t>
+          <t>HISTRS_c_FWD-rt0207_c</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>18568.45228640065</v>
+        <v>6690.323840326685</v>
       </c>
       <c r="C133" t="n">
-        <v>54382.54738474332</v>
+        <v>12705.94767687727</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>G3PAT_rm_FWD-rt7067</t>
+          <t>HMGCOAR_c_FWD-rt1206</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>18568.45228640065</v>
+        <v>65378.24283816044</v>
       </c>
       <c r="C134" t="n">
-        <v>54382.54738474332</v>
+        <v>305457.3080716128</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>G3PD1r_c_FWD-rt3786_c</t>
+          <t>HMGCOAS_c_FWD-rt3754_c</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>708616.7237750653</v>
+        <v>10145.79505075245</v>
       </c>
       <c r="C135" t="n">
-        <v>9344.084703333769</v>
+        <v>11291.61630071268</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>G3PD1r_c_FWD-rt6208_c</t>
+          <t>HSERTA_c_FWD-rt4145</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>708616.7237750653</v>
+        <v>101488.2297119603</v>
       </c>
       <c r="C136" t="n">
-        <v>9344.084703333769</v>
+        <v>30865.99361005156</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>G3PDf_m_FWD-rt2671</t>
+          <t>HSK_c_FWD-rt0283</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.2758302388716642</v>
+        <v>103363.803416035</v>
       </c>
       <c r="C137" t="n">
-        <v>22482.5659771631</v>
+        <v>106054.8685177949</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>G3PT_c_FWD-rt0092</t>
+          <t>HSTPT_c_FWD-rt4862</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>45873.17011132596</v>
+        <v>4203.002996823508</v>
       </c>
       <c r="C138" t="n">
-        <v>558757.9235695571</v>
+        <v>9266.650174693652</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>G5SDy_c_FWD-rt7905</t>
+          <t>ICDHx_m_FWD-IDH12</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>54049.6002045816</v>
+        <v>0.0517834058601942</v>
       </c>
       <c r="C139" t="n">
-        <v>1943.410632772637</v>
+        <v>642629.472105089</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>G6PDH2i_c_FWD-rt1632</t>
+          <t>IG3PS_c_FWD-rt0716</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>118557.538016746</v>
+        <v>4341.605613739696</v>
       </c>
       <c r="C140" t="n">
-        <v>237734.9906711836</v>
+        <v>8190.452451932022</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GALUi_c_FWD-rt3384</t>
+          <t>IGPDH_c_FWD-rt0339</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>846433.6170102324</v>
+        <v>6675.955662625822</v>
       </c>
       <c r="C141" t="n">
-        <v>37018.26683502624</v>
+        <v>25473.90896715222</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>GAPD_c_FWD-rt2245</t>
+          <t>IGPS_c_FWD-rt8196</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>716723.3803490424</v>
+        <v>90711.91737234942</v>
       </c>
       <c r="C142" t="n">
-        <v>306207.2051489567</v>
+        <v>24653.72712378941</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GAPD_c_FWD-rt3311</t>
+          <t>ILETRS_c_FWD-rt5078</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>716723.3803490424</v>
+        <v>14309.04320510554</v>
       </c>
       <c r="C143" t="n">
-        <v>306207.2051489567</v>
+        <v>15165.10446519942</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GARFT_c_FWD-rt5227</t>
+          <t>IMPC_c_FWD-rt4053</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>18606.44391043914</v>
+        <v>115517.9447339925</v>
       </c>
       <c r="C144" t="n">
-        <v>38571.30530576928</v>
+        <v>11862.19442861235</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GF6PTA_c_FWD-rt3731</t>
+          <t>IMPD_c_FWD-rt0027</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2699.558006705075</v>
+        <v>7537.504721009301</v>
       </c>
       <c r="C145" t="n">
-        <v>227728895809.7877</v>
+        <v>18346.28584203905</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GHMT2r_c_FWD-rt1299</t>
+          <t>INOSTtps_e_FWD-rt4674</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>132765.4032245435</v>
+        <v>1172.896064677279</v>
       </c>
       <c r="C146" t="n">
-        <v>127082.2937511697</v>
+        <v>20706067.7852834</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GK1_c_FWD-rt3157</t>
+          <t>IPDDI_c_FWD-rt7835</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4036.917936978396</v>
+        <v>9168.319799928102</v>
       </c>
       <c r="C147" t="n">
-        <v>5131.735167603132</v>
+        <v>15822.42617206315</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GK1_c_FWD-rt3670</t>
+          <t>IPMD_c_FWD-rt5526</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4036.917936978396</v>
+        <v>19003.55690345721</v>
       </c>
       <c r="C148" t="n">
-        <v>2898.763719462165</v>
+        <v>15988.46439470184</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>GLCt_c_e_FWD-rt2336</t>
+          <t>IPPMIa_c_REV-rt6546</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>5611787.457547248</v>
+        <v>24574.70360922258</v>
       </c>
       <c r="C149" t="n">
-        <v>9433717.303880269</v>
+        <v>38065.40425648049</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GLCt_c_e_FWD-rt2707</t>
+          <t>IPPMIb_c_REV-rt6546</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>5611787.457547248</v>
+        <v>24574.70360922258</v>
       </c>
       <c r="C150" t="n">
-        <v>797365.4145077304</v>
+        <v>38065.40425648049</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GLCt_c_e_FWD-rt2833</t>
+          <t>IPPS_c_FWD-rt7120</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>5611787.457547248</v>
+        <v>45114.83956157051</v>
       </c>
       <c r="C151" t="n">
-        <v>797365.4145077304</v>
+        <v>9105.163999747079</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GLCt_c_e_FWD-rt3556</t>
+          <t>KARA1i_m_FWD-rt0808</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>5611787.457547248</v>
+        <v>6862.440926644408</v>
       </c>
       <c r="C152" t="n">
-        <v>797365.4145077304</v>
+        <v>7709.049898961211</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GLCt_c_e_FWD-rt4674</t>
+          <t>KARA2i_m_FWD-rt0808</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>5611787.457547248</v>
+        <v>6862.440926644408</v>
       </c>
       <c r="C153" t="n">
-        <v>797365.4145077304</v>
+        <v>7709.049898961211</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>GLCt_c_e_FWD-rt7817</t>
+          <t>LEUTA_c_REV-rt5646</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>5611787.457547248</v>
+        <v>3039403.490921701</v>
       </c>
       <c r="C154" t="n">
-        <v>797365.4145077304</v>
+        <v>715765.3365758617</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GLNS_c_FWD-rt3476</t>
+          <t>LEUTRS_c_FWD-rt1776</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1103315.83553435</v>
+        <v>24631.78735694899</v>
       </c>
       <c r="C155" t="n">
-        <v>284419.8826598884</v>
+        <v>17773.91851715687</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>GLNTRS_c_FWD-rt5012</t>
+          <t>LYSTRS_c_FWD-rt3577</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>17315.47474321497</v>
+        <v>22766.53957257269</v>
       </c>
       <c r="C156" t="n">
-        <v>19235.45194197289</v>
+        <v>11921.46801522159</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>GLU5K_c_FWD-rt6820</t>
+          <t>MAN1PT_c_FWD-rt6588</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>205857.5251750045</v>
+        <v>4265.914713366408</v>
       </c>
       <c r="C157" t="n">
-        <v>22482.5659771631</v>
+        <v>10802.48139899952</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>GLUDC_c_FWD-rt1067</t>
+          <t>MAN6PI_c_REV-rt0239</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>381380.9132269296</v>
+        <v>17362.8549371627</v>
       </c>
       <c r="C158" t="n">
-        <v>22482.5659771631</v>
+        <v>35550.9136483504</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>GLUDC_c_FWD-rt2354</t>
+          <t>MDH_c_REV-rt2246</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>381380.9132269296</v>
+        <v>19547978.90913997</v>
       </c>
       <c r="C159" t="n">
-        <v>22482.5659771631</v>
+        <v>189184.8379177387</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>GLUDy_c_FWD-rt3880</t>
+          <t>MDH_m_FWD-rt2810</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>112672.3890786228</v>
+        <v>34107.30013435378</v>
       </c>
       <c r="C160" t="n">
-        <v>737991.7996802761</v>
+        <v>143182.0058175448</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>GLUPRT_c_FWD-rt6932</t>
+          <t>ME1_m_FWD-rt5549</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>10189.93477578383</v>
+        <v>228406.7382460386</v>
       </c>
       <c r="C161" t="n">
-        <v>23294.47852744794</v>
+        <v>496256.3610694612</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>GLUt_c_m_FWD-rt4150</t>
+          <t>METAT_c_FWD-rt5403</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1018791.951536927</v>
+        <v>2751.135674318203</v>
       </c>
       <c r="C162" t="n">
-        <v>1716395.706281398</v>
+        <v>1075.166790929645</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GLUt_c_m_FWD-rt8431</t>
+          <t>METS_c_FWD-rt1457</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1018791.951536927</v>
+        <v>651.0227337949582</v>
       </c>
       <c r="C163" t="n">
-        <v>1998797.875076495</v>
+        <v>1113.415141938496</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>GLUTRS_c_FWD-rt2385</t>
+          <t>METTRS_c_FWD-rt4772</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>29478.84880083635</v>
+        <v>6759.833997594901</v>
       </c>
       <c r="C164" t="n">
-        <v>22438.02319081071</v>
+        <v>12887.76335761611</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>GLYCL_m_FWD-GCV123LPD1</t>
+          <t>MEVK1_c_FWD-rt0390</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>244947.9411074351</v>
+        <v>78641.79360353248</v>
       </c>
       <c r="C165" t="n">
-        <v>716004.3617927532</v>
+        <v>20334.29238666278</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>GLYCtps_e_REV-rt2336</t>
+          <t>MTHFC_m_FWD-rt6998</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>18568.45228640065</v>
+        <v>1922045.616244709</v>
       </c>
       <c r="C166" t="n">
-        <v>9433717.303880269</v>
+        <v>134784.2998981823</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GLYGS_c_FWD-rt12285634</t>
+          <t>MTHFD2i_c_FWD-rt4257</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1071109.175293076</v>
+        <v>0.0388117813996373</v>
       </c>
       <c r="C167" t="n">
-        <v>234143.4419839105</v>
+        <v>1357416.898328512</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GLYOX_c_FWD-rt4673</t>
+          <t>MTHFD_c_FWD-rt6998</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.1008300116242537</v>
+        <v>439442.6375940125</v>
       </c>
       <c r="C168" t="n">
-        <v>25179.0935824534</v>
+        <v>134784.2998981823</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GLYt_c_m_FWD-rt0066</t>
+          <t>MTHFD_m_FWD-rt6998</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>709928.077312314</v>
+        <v>1922045.616244709</v>
       </c>
       <c r="C169" t="n">
-        <v>1219930.179784989</v>
+        <v>134784.2998981823</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>GLYt_c_m_FWD-rt4150</t>
+          <t>MTHFR3_c_FWD-MET1213</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>709928.077312314</v>
+        <v>13137.11180539718</v>
       </c>
       <c r="C170" t="n">
-        <v>1716395.706281398</v>
+        <v>48801.44503882494</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>GLYTRS_c_FWD-rt7136</t>
+          <t>NACt_c_e_FWD-rt3853</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>22748.03085129843</v>
+        <v>20312.93959930927</v>
       </c>
       <c r="C171" t="n">
-        <v>17924.20676148744</v>
+        <v>28535.93651395841</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GND_c_FWD-rt2224</t>
+          <t>NADK_c_FWD-rt1814_c</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>32686.12794724121</v>
+        <v>367496.1097064805</v>
       </c>
       <c r="C172" t="n">
-        <v>136070.6266998698</v>
+        <v>3026.742796367941</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GND_c_FWD-rt6799</t>
+          <t>NADS2_c_FWD-rt0915_c</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>32686.12794724121</v>
+        <v>1606.507613279945</v>
       </c>
       <c r="C173" t="n">
-        <v>136070.6266998698</v>
+        <v>866.3342139193377</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GRTT_c_FWD-rt4576</t>
+          <t>NAMNPP_c_FWD-rt1924_c</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>5319.136842925104</v>
+        <v>525.5297743074007</v>
       </c>
       <c r="C174" t="n">
-        <v>18294.1396263311</v>
+        <v>322.1734190875059</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HACNH_m_FWD-rt3256</t>
+          <t>NDPK1_c_FWD-rt7311</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>41659.54469771364</v>
+        <v>1585861.208793881</v>
       </c>
       <c r="C175" t="n">
-        <v>236508.8303380169</v>
+        <v>58226.06456454589</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HACNH_m_FWD-rt6232</t>
+          <t>NDPK2_c_FWD-rt7311</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>41659.54469771364</v>
+        <v>1585861.208793881</v>
       </c>
       <c r="C176" t="n">
-        <v>2035976.004420073</v>
+        <v>58226.06456454589</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HACNH_m_FWD-rt7648</t>
+          <t>NDPK3_c_FWD-rt7311</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>41659.54469771364</v>
+        <v>1585861.208793881</v>
       </c>
       <c r="C177" t="n">
-        <v>48351.53531961972</v>
+        <v>58226.06456454589</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HCITR_m_FWD-rt7648</t>
+          <t>NDPK4_c_FWD-rt7311</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>41659.54469771364</v>
+        <v>1585861.208793881</v>
       </c>
       <c r="C178" t="n">
-        <v>48351.53531961972</v>
+        <v>58226.06456454589</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HCITS_m_FWD-rt6488_m</t>
+          <t>NDPK5_c_FWD-rt7311</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7502.871322486296</v>
+        <v>1585861.208793881</v>
       </c>
       <c r="C179" t="n">
-        <v>5171.912945977572</v>
+        <v>58226.06456454589</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HCO3E_c_FWD-rt4213</t>
+          <t>NDPK6_c_FWD-rt7311</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>622936.8010802376</v>
+        <v>1585861.208793881</v>
       </c>
       <c r="C180" t="n">
-        <v>326738.2079836217</v>
+        <v>58226.06456454589</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HEX1_c_FWD-rt1896</t>
+          <t>NDPK7_c_FWD-rt7311</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1266756.205724464</v>
+        <v>1585861.208793881</v>
       </c>
       <c r="C181" t="n">
-        <v>372294.0050249592</v>
+        <v>58226.06456454589</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HEX1_c_FWD-rt3614</t>
+          <t>NH4t_c_e_FWD-rt4558</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1266756.205724464</v>
+        <v>3539615.577823241</v>
       </c>
       <c r="C182" t="n">
-        <v>372294.0050249592</v>
+        <v>2634329.732969249</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HICITD_m_FWD-rt2060</t>
+          <t>NNATi_c_FWD-rt2062_c</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>6590.732743703376</v>
+        <v>10974.54526734059</v>
       </c>
       <c r="C183" t="n">
-        <v>5425.088462608715</v>
+        <v>2750.717565592221</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HISTD_c_FWD-rt3278</t>
+          <t>OCBT_c_FWD-rt4934</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>5784.712267411584</v>
+        <v>10954.3060794853</v>
       </c>
       <c r="C184" t="n">
-        <v>37387.05249008304</v>
+        <v>13784.07697006268</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HISTP_c_FWD-rt1838</t>
+          <t>OMCDC_c_FWD-rt5646</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>77451.78284265276</v>
+        <v>3039403.490921701</v>
       </c>
       <c r="C185" t="n">
-        <v>115229.6968599392</v>
+        <v>715765.3365758617</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HISTRS_c_FWD-rt0207_c</t>
+          <t>OMPDC_c_FWD-rt3750</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>6690.323840326668</v>
+        <v>12481.96694581984</v>
       </c>
       <c r="C186" t="n">
-        <v>12677.89247835962</v>
+        <v>13580.11874910694</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HMGCOAR_c_FWD-rt1206</t>
+          <t>ORNTACi_m_FWD-rt7840</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>65378.24283816037</v>
+        <v>123794.4545820929</v>
       </c>
       <c r="C187" t="n">
-        <v>305457.3067474923</v>
+        <v>63669.69347329832</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HMGCOAS_c_FWD-rt3754_c</t>
+          <t>ORNTA_c_FWD-rt6698</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>10145.79505075244</v>
+        <v>408470.4605950536</v>
       </c>
       <c r="C188" t="n">
-        <v>11291.61625176488</v>
+        <v>14596.29563587165</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HSERTA_c_FWD-rt4145</t>
+          <t>ORNtpa_m_FWD-rt4951</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>101488.22971196</v>
+        <v>719912.1853378712</v>
       </c>
       <c r="C189" t="n">
-        <v>40204.09801834812</v>
+        <v>1341108.471833471</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HSK_c_FWD-rt0283</t>
+          <t>ORPT_c_REV-rt2348</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>103363.8034160347</v>
+        <v>8355.915929480978</v>
       </c>
       <c r="C190" t="n">
-        <v>98835.81576680412</v>
+        <v>18204.99152875068</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HSTPT_c_FWD-rt4862</t>
+          <t>P5CR_c_FWD-rt5064</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>4203.002996823492</v>
+        <v>230379.6094380761</v>
       </c>
       <c r="C191" t="n">
-        <v>9246.189071212344</v>
+        <v>20292.8143349393</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ICDHx_m_FWD-IDH12</t>
+          <t>PAILS_rm_FWD-rt6753</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.05178340586019421</v>
+        <v>1620.162482022008</v>
       </c>
       <c r="C192" t="n">
-        <v>533346.0729391188</v>
+        <v>2867.704070690285</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>IG3PS_c_FWD-rt0716</t>
+          <t>PAPSR_c_FWD-MET16TRX1</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>4341.605613739668</v>
+        <v>18597.00763960596</v>
       </c>
       <c r="C193" t="n">
-        <v>8254.916800501931</v>
+        <v>25116.92492177307</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>IGPDH_c_FWD-rt0339</t>
+          <t>PAP_rm_FWD-rt4117</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>6675.955662625813</v>
+        <v>1702985.965964656</v>
       </c>
       <c r="C194" t="n">
-        <v>25417.66164178395</v>
+        <v>17584.77389921688</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>IGPS_c_FWD-rt8196</t>
+          <t>PC_c_FWD-rt7325</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>90711.91737234936</v>
+        <v>1059980.412103982</v>
       </c>
       <c r="C195" t="n">
-        <v>65544.18765609564</v>
+        <v>82709.65730816941</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ILETRS_c_FWD-rt5078</t>
+          <t>PDH_m_FWD-PDHCPLX</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>14309.04320510551</v>
+        <v>821072.8584994342</v>
       </c>
       <c r="C196" t="n">
-        <v>15140.91764821986</v>
+        <v>717013.7387081676</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>IMPC_c_FWD-rt4053</t>
+          <t>PDMEMT_rm_FWD-rt4380</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>115517.9447339926</v>
+        <v>18351.36561837213</v>
       </c>
       <c r="C197" t="n">
-        <v>11857.01098512841</v>
+        <v>6267.924729273573</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>IMPD_c_FWD-rt0027</t>
+          <t>PEMT_rm_FWD-rt4380</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>7537.504721009293</v>
+        <v>12217.22775769034</v>
       </c>
       <c r="C198" t="n">
-        <v>18351.63362857363</v>
+        <v>6267.924729273573</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>IPDDI_c_FWD-rt7835</t>
+          <t>PFK_c_FWD-rt0499</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>9168.319799938728</v>
+        <v>10805534.25544178</v>
       </c>
       <c r="C199" t="n">
-        <v>15822.42610347482</v>
+        <v>11346447.07163966</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>IPMD_c_FWD-rt5526</t>
+          <t>PGCD_c_FWD-rt3683</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>19003.5569034572</v>
+        <v>50285.00300625149</v>
       </c>
       <c r="C200" t="n">
-        <v>16017.84013067626</v>
+        <v>8397435.7557679</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>IPPMIa_c_REV-rt6546</t>
+          <t>PGI_c_FWD-rt1221</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>24574.70360922257</v>
+        <v>3136270.287023882</v>
       </c>
       <c r="C201" t="n">
-        <v>38135.34213403968</v>
+        <v>95435.51272773321</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>IPPMIb_c_REV-rt6546</t>
+          <t>PGK_c_FWD-rt7353</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>24574.70360922257</v>
+        <v>413350.4238899917</v>
       </c>
       <c r="C202" t="n">
-        <v>38135.34213403968</v>
+        <v>272791.2766911988</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>IPPS_c_FWD-rt7120</t>
+          <t>PGL_c_FWD-rt6131</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>45114.8395615704</v>
+        <v>132153.2708387187</v>
       </c>
       <c r="C203" t="n">
-        <v>9121.892991791436</v>
+        <v>295282.8095742577</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>KARA1i_m_FWD-rt0808</t>
+          <t>PGMT_c_FWD-rt1591</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>6862.44092664438</v>
+        <v>368557.1356618343</v>
       </c>
       <c r="C204" t="n">
-        <v>7720.127413490556</v>
+        <v>30883.86123060002</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>KARA2i_m_FWD-rt0808</t>
+          <t>PGM_c_FWD-rt1542</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>6862.44092664438</v>
+        <v>2200782.159690033</v>
       </c>
       <c r="C205" t="n">
-        <v>7720.127413490556</v>
+        <v>116947.8106102277</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>KYN_c_FWD-rt0357</t>
+          <t>PHETA1_c_REV-rt7471</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>437903.6068186344</v>
+        <v>61343.54779923162</v>
       </c>
       <c r="C206" t="n">
-        <v>267198.6179108229</v>
+        <v>417154.8823556802</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>LALDO3_c_FWD-rt3783</t>
+          <t>PHETRS_c_FWD-FRS12</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1572.213483084244</v>
+        <v>25358.25152147787</v>
       </c>
       <c r="C207" t="n">
-        <v>22482.5659771631</v>
+        <v>25428.43044849215</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>LCADi_c_FWD-rt3783</t>
+          <t>PItps_e_FWD-rt1948</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>8157.778994769839</v>
+        <v>1038731.677507144</v>
       </c>
       <c r="C208" t="n">
-        <v>22482.5659771631</v>
+        <v>1809691.260738617</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>LEUTA_c_REV-rt5646</t>
+          <t>PItps_m_FWD-rt0521</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3039403.4909217</v>
+        <v>421028.7470406002</v>
       </c>
       <c r="C209" t="n">
-        <v>717080.4180638532</v>
+        <v>1896676.876475679</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LEUTRS_c_FWD-rt1776</t>
+          <t>PMANM_c_REV-rt0873</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>24631.78735694898</v>
+        <v>31732.01575719642</v>
       </c>
       <c r="C210" t="n">
-        <v>17806.57468254598</v>
+        <v>22671.38110398814</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LGTHL_c_FWD-rt4897</t>
+          <t>PMEMT_rm_FWD-rt4380</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.1832021970487499</v>
+        <v>18351.36561837213</v>
       </c>
       <c r="C211" t="n">
-        <v>22482.5659771631</v>
+        <v>6267.924729273573</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>LLFC2O_c_FWD-rt0745</t>
+          <t>PMEVK_c_FWD-rt0334</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>81660.50062206083</v>
+        <v>72800.83279883592</v>
       </c>
       <c r="C212" t="n">
-        <v>0.1980566348348034</v>
+        <v>210911.4837541752</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LLFC2O_c_FWD-rt8239</t>
+          <t>PNTK_c_FWD-rt5817</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>81660.50062206083</v>
+        <v>59.88607986242029</v>
       </c>
       <c r="C213" t="n">
-        <v>0.1980566348348034</v>
+        <v>0.0034279218251179</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LYSTRS_c_FWD-rt3577</t>
+          <t>PNTOtps_e_FWD-rt3985</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>22766.53957257269</v>
+        <v>6815.185800074178</v>
       </c>
       <c r="C214" t="n">
-        <v>11910.93433155176</v>
+        <v>1.069049893965407</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MAN1PT_c_FWD-rt6588</t>
+          <t>PPA_c_FWD-rt7511</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>4265.914713366384</v>
+        <v>60630.06806424595</v>
       </c>
       <c r="C215" t="n">
-        <v>10802.4813989995</v>
+        <v>88418.80962056642</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MAN6PI_c_REV-rt0239</t>
+          <t>PPBNGD_c_FWD-rt6350</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>17362.85493716269</v>
+        <v>13.39213889663197</v>
       </c>
       <c r="C216" t="n">
-        <v>35910.01378621253</v>
+        <v>31.68917045364363</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MDH_c_REV-rt2246</t>
+          <t>PPBNGS_1_c_FWD-rt5026</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>19547978.90913997</v>
+        <v>113.3004329172821</v>
       </c>
       <c r="C217" t="n">
-        <v>297094.0083301688</v>
+        <v>126.0714221902509</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MDH_m_FWD-rt2810</t>
+          <t>PPCDC_c_FWD-rt0168</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>34107.30013435376</v>
+        <v>259.8114779535934</v>
       </c>
       <c r="C218" t="n">
-        <v>179626.5132122999</v>
+        <v>37095.08928294634</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ME1_m_FWD-rt5549</t>
+          <t>PPNCL2_c_FWD-rt0510</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>228406.7382460384</v>
+        <v>117.6730722504989</v>
       </c>
       <c r="C219" t="n">
-        <v>578844.8862588216</v>
+        <v>0.0013554373646061</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>METAT_c_FWD-rt5403</t>
+          <t>PPND2_c_FWD-rt7857</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2751.135674318201</v>
+        <v>59613.63084289849</v>
       </c>
       <c r="C220" t="n">
-        <v>1075.223377399122</v>
+        <v>54267.77964563397</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>METB1_c_FWD-rt3095</t>
+          <t>PPNDH_c_FWD-rt5827</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>463824.4729282848</v>
+        <v>114730.1208833828</v>
       </c>
       <c r="C221" t="n">
-        <v>10.90054727001047</v>
+        <v>347882.7752964782</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>METB1_c_FWD-rt8357</t>
+          <t>PPPGO_m_FWD-rt3499</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>463824.4729282848</v>
+        <v>14.37232740114392</v>
       </c>
       <c r="C222" t="n">
-        <v>10.90054727001047</v>
+        <v>20.24525047523658</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>METB1_c_FWD-rt8374</t>
+          <t>PRAGSi_c_FWD-rt5891</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>463824.4729282848</v>
+        <v>4674.2284213981</v>
       </c>
       <c r="C223" t="n">
-        <v>10.90054727001047</v>
+        <v>15560.23443154606</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>METS_c_FWD-rt1457</t>
+          <t>PRAIS_c_FWD-rt5891</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>651.0227337949572</v>
+        <v>4674.2284213981</v>
       </c>
       <c r="C224" t="n">
-        <v>1114.195761565888</v>
+        <v>15560.23443154606</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>METTRS_c_FWD-rt4772</t>
+          <t>PRAIi_c_FWD-rt8196</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>6759.833997594888</v>
+        <v>345804.2166722123</v>
       </c>
       <c r="C225" t="n">
-        <v>13040.65496151076</v>
+        <v>24653.72712378941</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MEVK1_c_FWD-rt0390</t>
+          <t>PRAMPC_c_FWD-rt3278</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>78641.79360353244</v>
+        <v>5784.712267411606</v>
       </c>
       <c r="C226" t="n">
-        <v>20539.68919042028</v>
+        <v>37095.08928294634</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MTHFC_m_FWD-rt6998</t>
+          <t>PRASCSi_c_FWD-rt0852</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1922045.616244706</v>
+        <v>4192.712672048641</v>
       </c>
       <c r="C227" t="n">
-        <v>180540.2352900261</v>
+        <v>9070.49724261196</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>MTHFD_c_FWD-rt6998</t>
+          <t>PRATPP_c_FWD-rt3278</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>439442.637594012</v>
+        <v>5784.712267411606</v>
       </c>
       <c r="C228" t="n">
-        <v>180540.2352900261</v>
+        <v>37095.08928294634</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MTHFD_m_FWD-rt6998</t>
+          <t>PRFGS_c_FWD-rt6665</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1922045.616244706</v>
+        <v>5254.227782418362</v>
       </c>
       <c r="C229" t="n">
-        <v>180540.2352900261</v>
+        <v>12325.48132579605</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MTHFD2i_c_FWD-rt4257</t>
+          <t>PRMICI_c_FWD-rt3242_c</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.03881178139963716</v>
+        <v>54146.89640687814</v>
       </c>
       <c r="C230" t="n">
-        <v>1615229.804131657</v>
+        <v>20885.08636734653</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MTHFR3_c_FWD-MET1213</t>
+          <t>PROTRS_c_FWD-rt3118</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>13137.11180539718</v>
+        <v>10629.86208393305</v>
       </c>
       <c r="C231" t="n">
-        <v>48835.659919158</v>
+        <v>5386.275324843459</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NACt_c_e_FWD-rt3853</t>
+          <t>PRPPS_c_FWD-PRS23</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>20312.93959930926</v>
+        <v>51693.97663725622</v>
       </c>
       <c r="C232" t="n">
-        <v>28535.93651424082</v>
+        <v>79002.97455031535</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NADK_c_FWD-rt1814_c</t>
+          <t>PSCIT_c_FWD-rt5884</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>367496.1097064784</v>
+        <v>265929.8632596141</v>
       </c>
       <c r="C233" t="n">
-        <v>3026.742796542557</v>
+        <v>291580.9706850972</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NADS2_c_FWD-rt0915_c</t>
+          <t>PSD_mm_FWD-rt2136</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1606.507613279942</v>
+        <v>18440.14401846416</v>
       </c>
       <c r="C234" t="n">
-        <v>866.3342139279108</v>
+        <v>10060.98942899159</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>NAMNPP_c_FWD-rt1924_c</t>
+          <t>PSERT_c_FWD-rt7036</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>525.5297743073976</v>
+        <v>247772.3163618335</v>
       </c>
       <c r="C235" t="n">
-        <v>322.1734190906944</v>
+        <v>533762.5564808153</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>NDPK1_c_FWD-rt7311</t>
+          <t>PSP_L_c_FWD-rt3683</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1585861.208790012</v>
+        <v>669122.1223448976</v>
       </c>
       <c r="C236" t="n">
-        <v>58189.76272460556</v>
+        <v>8397435.7557679</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>NDPK2_c_FWD-rt7311</t>
+          <t>PSSA_rm_FWD-rt3215</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1585861.208790012</v>
+        <v>7142.137923422562</v>
       </c>
       <c r="C237" t="n">
-        <v>58189.76272460556</v>
+        <v>63329.57560262542</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>NDPK3_c_FWD-rt7311</t>
+          <t>PYK_c_FWD-rt4634</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1585861.208790012</v>
+        <v>1852523.275282808</v>
       </c>
       <c r="C238" t="n">
-        <v>58189.76272460556</v>
+        <v>125792.9206506753</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>NDPK4_c_FWD-rt7311</t>
+          <t>PYRtps_m_FWD-MPC13</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1585861.208790012</v>
+        <v>314030.9772923344</v>
       </c>
       <c r="C239" t="n">
-        <v>58189.76272460556</v>
+        <v>143900261179767.4</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>NDPK5_c_FWD-rt7311</t>
+          <t>RBFK_c_FWD-rt0930_c</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1585861.208790012</v>
+        <v>35.67006327169954</v>
       </c>
       <c r="C240" t="n">
-        <v>58189.76272460556</v>
+        <v>8.092604541709713</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NDPK7_c_FWD-rt7311</t>
+          <t>RNDR1_c_FWD-RNR124</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1585861.208790012</v>
+        <v>2171.805849089208</v>
       </c>
       <c r="C241" t="n">
-        <v>58189.76272460556</v>
+        <v>25908.18570643674</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>NH4t_c_e_FWD-rt4558</t>
+          <t>RNDR2_c_FWD-RNR124</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>3539615.577823238</v>
+        <v>2171.805849089208</v>
       </c>
       <c r="C242" t="n">
-        <v>2633646.557879219</v>
+        <v>25908.18570643674</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>NNATi_c_FWD-rt2062_c</t>
+          <t>RNDR3_c_FWD-RNR124</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>10974.54526734056</v>
+        <v>2171.805849089208</v>
       </c>
       <c r="C243" t="n">
-        <v>2750.717565510545</v>
+        <v>25908.18570643674</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>OAAtps_m_FWD-rt0643</t>
+          <t>RPE_c_FWD-rt3505</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>87437.73590311968</v>
+        <v>208487.2424236493</v>
       </c>
       <c r="C244" t="n">
-        <v>22482.5659771631</v>
+        <v>900160.7098055375</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>OCBT_c_FWD-rt4934</t>
+          <t>RPI_c_FWD-rt4920</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>10954.30607948527</v>
+        <v>164516.16087793</v>
       </c>
       <c r="C245" t="n">
-        <v>13902.51479162756</v>
+        <v>371009.017153045</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>OMCDC_c_FWD-rt5646</t>
+          <t>SACCD1_c_FWD-rt8465</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>3039403.4909217</v>
+        <v>5174.934352000321</v>
       </c>
       <c r="C246" t="n">
-        <v>717080.4180638532</v>
+        <v>15117.71190980087</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>OMPDC_c_FWD-rt3750</t>
+          <t>SACCD2_c_FWD-rt8465</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>12481.96694581984</v>
+        <v>11964.02100059463</v>
       </c>
       <c r="C247" t="n">
-        <v>13580.21568043948</v>
+        <v>15117.71190980087</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ORNTA_c_FWD-rt6698</t>
+          <t>SADT_c_FWD-rt5075</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>408470.4605950524</v>
+        <v>15583.98616093314</v>
       </c>
       <c r="C248" t="n">
-        <v>21869.96181781565</v>
+        <v>20654.26083107627</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ORNTACi_m_FWD-rt7840</t>
+          <t>SAM24MT_c_FWD-rt4692</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>123794.4545820929</v>
+        <v>867.9010017353345</v>
       </c>
       <c r="C249" t="n">
-        <v>204069.7756581732</v>
+        <v>6572.834013574223</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ORNtpa_m_FWD-rt4951</t>
+          <t>SERAT_c_FWD-rt6880</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>719912.1853378692</v>
+        <v>23194.46883722089</v>
       </c>
       <c r="C250" t="n">
-        <v>1652622.020997048</v>
+        <v>30594.54047635072</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ORPT_c_REV-rt2348</t>
+          <t>SERTRS_c_FWD-rt1878</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>8355.915929480976</v>
+        <v>16073.67819388007</v>
       </c>
       <c r="C251" t="n">
-        <v>18389.01158708529</v>
+        <v>14740.62911320013</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>P5CR_c_FWD-rt5064</t>
+          <t>SHCHD2_c_FWD-rt5201</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>230379.6094380759</v>
+        <v>17.05502661307044</v>
       </c>
       <c r="C252" t="n">
-        <v>36689.06458690452</v>
+        <v>23.40496549416282</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PAILS_rm_FWD-rt6753</t>
+          <t>SHCHF_c_FWD-rt5201</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>1620.162482022007</v>
+        <v>17.05502661307044</v>
       </c>
       <c r="C253" t="n">
-        <v>2867.704070690282</v>
+        <v>23.40496549416282</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PAP_rm_FWD-rt4117</t>
+          <t>SHK3Di_c_FWD-rt5884</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>1702985.965964654</v>
+        <v>265929.8632596141</v>
       </c>
       <c r="C254" t="n">
-        <v>17584.77389921687</v>
+        <v>291580.9706850972</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PAPSR_c_FWD-MET16TRX1</t>
+          <t>SHKK_c_FWD-rt5884</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>18597.00763960596</v>
+        <v>265929.8632596141</v>
       </c>
       <c r="C255" t="n">
-        <v>25133.63654655029</v>
+        <v>291580.9706850972</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PAPSR_c_FWD-MET16TRX2</t>
+          <t>SO3R_c_FWD-rt20063076</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>18597.00763960596</v>
+        <v>9980.836169543039</v>
       </c>
       <c r="C256" t="n">
-        <v>25133.63654655029</v>
+        <v>24389.21141308535</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PC_c_FWD-rt7325</t>
+          <t>SO4t_c_e_FWD-rt7368</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1059980.412103981</v>
+        <v>132289.708308498</v>
       </c>
       <c r="C257" t="n">
-        <v>88790.40375383917</v>
+        <v>293211.5014866447</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PC_c_FWD-rt8262</t>
+          <t>SUCOAS_m_FWD-LSC12</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1059980.412103981</v>
+        <v>93890.19007389712</v>
       </c>
       <c r="C258" t="n">
-        <v>88790.40375383917</v>
+        <v>155630.891619641</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PDH_m_FWD-PDHCPLX</t>
+          <t>TALA_c_FWD-rt1805</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>821072.858499432</v>
+        <v>35667.14969737249</v>
       </c>
       <c r="C259" t="n">
-        <v>575837.565922152</v>
+        <v>15017.42839789238</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PDMEMT_rm_FWD-rt4380</t>
+          <t>THRD_L_m_FWD-rt3541</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>18351.36561837211</v>
+        <v>273968804381.2529</v>
       </c>
       <c r="C260" t="n">
-        <v>6267.924729273564</v>
+        <v>62896.63146717341</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PEMT_rm_FWD-rt2279</t>
+          <t>THRS_c_FWD-rt1374</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>12217.22775769032</v>
+        <v>32807.9791964011</v>
       </c>
       <c r="C261" t="n">
-        <v>1713.959873499355</v>
+        <v>25398.06643284929</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PEMT_rm_FWD-rt4380</t>
+          <t>THRTRS_c_FWD-rt7480</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>12217.22775769032</v>
+        <v>12929.82164693064</v>
       </c>
       <c r="C262" t="n">
-        <v>6267.924729273564</v>
+        <v>15215.0624388073</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PFK_c_FWD-rt0499</t>
+          <t>TKT1_c_FWD-rt7263_c</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>10805534.25544177</v>
+        <v>1391006.830652198</v>
       </c>
       <c r="C263" t="n">
-        <v>10467494.0778285</v>
+        <v>190443.5221310508</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PGCD_c_FWD-rt0717</t>
+          <t>TKT2_c_FWD-rt7263_c</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>50285.00300614992</v>
+        <v>1391006.830652198</v>
       </c>
       <c r="C264" t="n">
-        <v>207395.0605603062</v>
+        <v>190443.5221310508</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PGCD_c_FWD-rt1147</t>
+          <t>TMDS_c_FWD-rt2477</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>50285.00300614992</v>
+        <v>1127.744227627964</v>
       </c>
       <c r="C265" t="n">
-        <v>207395.0605603062</v>
+        <v>976.2379336915044</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PGCD_c_FWD-rt3683</t>
+          <t>TPI_c_FWD-rt0932</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>50285.00300614992</v>
+        <v>517648.6715474528</v>
       </c>
       <c r="C266" t="n">
-        <v>9645831.756343259</v>
+        <v>288114.5579349769</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PGI_c_FWD-rt1221</t>
+          <t>TRDR_c_FWD-rt1320</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>3136270.287023881</v>
+        <v>6943.233968803538</v>
       </c>
       <c r="C267" t="n">
-        <v>85983.46543863576</v>
+        <v>8331.446687358641</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PGK_c_FWD-rt7353</t>
+          <t>TRE6PP_c_FWD-TPS12TSL1</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>413350.4238899904</v>
+        <v>39658.69269405196</v>
       </c>
       <c r="C268" t="n">
-        <v>253748.9395582581</v>
+        <v>66475.92980683938</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PGL_c_FWD-rt6131</t>
+          <t>TRE6PS_c_FWD-TPS12TSL1</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>132153.2708387184</v>
+        <v>39658.69269405196</v>
       </c>
       <c r="C269" t="n">
-        <v>294705.5788528603</v>
+        <v>66475.92980683938</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PGM_c_FWD-rt1542</t>
+          <t>TRPS1_c_FWD-rt0894</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>2200782.159690034</v>
+        <v>14929.4585127533</v>
       </c>
       <c r="C270" t="n">
-        <v>99216.50245279416</v>
+        <v>4275.949166423364</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PGM_c_FWD-rt7057</t>
+          <t>TRPTRS_c_FWD-rt6341</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>2200782.159690034</v>
+        <v>8968.76481861305</v>
       </c>
       <c r="C271" t="n">
-        <v>99216.50245279416</v>
+        <v>3485.632055964887</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PGMT_c_FWD-rt1591</t>
+          <t>TYRTA_c_FWD-rt7471</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>194507.143397118</v>
+        <v>61343.54779923162</v>
       </c>
       <c r="C272" t="n">
-        <v>30883.86123060002</v>
+        <v>417154.8823556802</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PHETA1_c_REV-rt1784_c</t>
+          <t>TYRTRS_c_FWD-rt8273</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>61343.54779923144</v>
+        <v>19825.37488439063</v>
       </c>
       <c r="C273" t="n">
-        <v>11201.2750148314</v>
+        <v>10317.17186237736</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PHETA1_c_REV-rt7471</t>
+          <t>UAGDP_c_FWD-rt0711</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>61343.54779923144</v>
+        <v>3645.338254921098</v>
       </c>
       <c r="C274" t="n">
-        <v>417809.4145928964</v>
+        <v>1707.657512128075</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PHETA1_c_REV-rt7697</t>
+          <t>UMPK_c_FWD-rt4822_c</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>61343.54779923144</v>
+        <v>26876.92699492519</v>
       </c>
       <c r="C275" t="n">
-        <v>22673.76654537086</v>
+        <v>30320.85680232815</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PHETRS_c_FWD-FRS12</t>
+          <t>UPP3MT_2_c_FWD-rt2682</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>25358.25152147785</v>
+        <v>3.063705750348399</v>
       </c>
       <c r="C276" t="n">
-        <v>25534.80335833718</v>
+        <v>7.03078869533853</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PItps_e_FWD-rt1948</t>
+          <t>UPP3S_c_FWD-rt2147</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>834091.6741741763</v>
+        <v>26.261986486163</v>
       </c>
       <c r="C277" t="n">
-        <v>1809986.060840573</v>
+        <v>37095.08928294634</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PItps_m_FWD-rt0521</t>
+          <t>UPPDC1_c_FWD-rt5811</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>421028.7470406</v>
+        <v>16.85490226350404</v>
       </c>
       <c r="C278" t="n">
-        <v>1871401.065347949</v>
+        <v>9.357434468840946</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PItps_m_FWD-rt7506</t>
+          <t>VALTA_c_FWD-rt5646</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>421028.7470406</v>
+        <v>3039403.490921701</v>
       </c>
       <c r="C279" t="n">
-        <v>1871401.065347949</v>
+        <v>715765.3365758617</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PMANM_c_REV-rt0873</t>
+          <t>VALTA_m_REV-rt6242_m</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>31732.01575719638</v>
+        <v>47302.57888388872</v>
       </c>
       <c r="C280" t="n">
-        <v>22671.38110398811</v>
+        <v>6344854678456.797</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PMEMT_rm_FWD-rt4380</t>
+          <t>VALTRS_c_FWD-rt8160_c</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>18351.36561837211</v>
+        <v>18299.22961483772</v>
       </c>
       <c r="C281" t="n">
-        <v>6267.924729273564</v>
+        <v>27586.65993079756</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PMEVK_c_FWD-rt0334</t>
+          <t>YUMPS_c_FWD-rt6068</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>72800.83279883592</v>
+        <v>2.005425259137805e-12</v>
       </c>
       <c r="C282" t="n">
-        <v>210911.4828398992</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>PNTK_c_FWD-rt5817</t>
-        </is>
-      </c>
-      <c r="B283" t="n">
-        <v>59.88607986242017</v>
-      </c>
-      <c r="C283" t="n">
-        <v>1.783268935734075</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>PNTOtps_e_FWD-rt3985</t>
-        </is>
-      </c>
-      <c r="B284" t="n">
-        <v>6815.185800074172</v>
-      </c>
-      <c r="C284" t="n">
-        <v>556.1397149407093</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>PPA_c_FWD-rt7511</t>
-        </is>
-      </c>
-      <c r="B285" t="n">
-        <v>60630.06806424577</v>
-      </c>
-      <c r="C285" t="n">
-        <v>90711.39167855316</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>PPCDC_c_FWD-rt0168</t>
-        </is>
-      </c>
-      <c r="B286" t="n">
-        <v>259.8114779535931</v>
-      </c>
-      <c r="C286" t="n">
-        <v>31529141.50279284</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>PPNCL2_c_FWD-rt0510</t>
-        </is>
-      </c>
-      <c r="B287" t="n">
-        <v>117.6730722504986</v>
-      </c>
-      <c r="C287" t="n">
-        <v>0.7051238242728047</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>PPND2_c_FWD-rt7857</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>59613.63084289837</v>
-      </c>
-      <c r="C288" t="n">
-        <v>54675.29156334337</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>PPNDH_c_FWD-rt5827</t>
-        </is>
-      </c>
-      <c r="B289" t="n">
-        <v>114730.1208833828</v>
-      </c>
-      <c r="C289" t="n">
-        <v>349338.0480931306</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>PRAGSi_c_FWD-rt5891</t>
-        </is>
-      </c>
-      <c r="B290" t="n">
-        <v>4674.228421398085</v>
-      </c>
-      <c r="C290" t="n">
-        <v>15565.28001539332</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>PRAIi_c_FWD-rt8196</t>
-        </is>
-      </c>
-      <c r="B291" t="n">
-        <v>345804.2166722123</v>
-      </c>
-      <c r="C291" t="n">
-        <v>65544.18765609564</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>PRAIS_c_FWD-rt5891</t>
-        </is>
-      </c>
-      <c r="B292" t="n">
-        <v>4674.228421398085</v>
-      </c>
-      <c r="C292" t="n">
-        <v>15565.28001539332</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>PRAMPC_c_FWD-rt3278</t>
-        </is>
-      </c>
-      <c r="B293" t="n">
-        <v>5784.712267411584</v>
-      </c>
-      <c r="C293" t="n">
-        <v>37387.05249008304</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>PRASCSi_c_FWD-rt0852</t>
-        </is>
-      </c>
-      <c r="B294" t="n">
-        <v>4192.712672048639</v>
-      </c>
-      <c r="C294" t="n">
-        <v>9165.089348491536</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>PRATPP_c_FWD-rt3278</t>
-        </is>
-      </c>
-      <c r="B295" t="n">
-        <v>5784.712267411584</v>
-      </c>
-      <c r="C295" t="n">
-        <v>37387.05249008304</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>PRFGS_c_FWD-rt6665</t>
-        </is>
-      </c>
-      <c r="B296" t="n">
-        <v>5254.227782418348</v>
-      </c>
-      <c r="C296" t="n">
-        <v>12329.47800397984</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>PRMICI_c_FWD-rt3242_c</t>
-        </is>
-      </c>
-      <c r="B297" t="n">
-        <v>54146.89640687796</v>
-      </c>
-      <c r="C297" t="n">
-        <v>20838.97133059406</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>PROD2_m_FWD-rt6234</t>
-        </is>
-      </c>
-      <c r="B298" t="n">
-        <v>1449177.045315358</v>
-      </c>
-      <c r="C298" t="n">
-        <v>10768579.11737946</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>PROTRS_c_FWD-rt3118</t>
-        </is>
-      </c>
-      <c r="B299" t="n">
-        <v>10629.86208393301</v>
-      </c>
-      <c r="C299" t="n">
-        <v>5384.057814884052</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>PRPPS_c_FWD-PRS23</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>51693.97663725588</v>
-      </c>
-      <c r="C300" t="n">
-        <v>146403.940348494</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>PSCIT_c_FWD-rt5884</t>
-        </is>
-      </c>
-      <c r="B301" t="n">
-        <v>265929.863259614</v>
-      </c>
-      <c r="C301" t="n">
-        <v>292550.0526924005</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>PSD_mm_FWD-rt2136</t>
-        </is>
-      </c>
-      <c r="B302" t="n">
-        <v>18440.14401846414</v>
-      </c>
-      <c r="C302" t="n">
-        <v>10060.98942899156</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>PSD_mm_FWD-rt6186</t>
-        </is>
-      </c>
-      <c r="B303" t="n">
-        <v>18440.14401846414</v>
-      </c>
-      <c r="C303" t="n">
-        <v>10060.98942899156</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>PSERT_c_FWD-rt7036</t>
-        </is>
-      </c>
-      <c r="B304" t="n">
-        <v>247772.3163618334</v>
-      </c>
-      <c r="C304" t="n">
-        <v>741302.1578036267</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>PSP_L_c_FWD-rt3683</t>
-        </is>
-      </c>
-      <c r="B305" t="n">
-        <v>669122.1223448976</v>
-      </c>
-      <c r="C305" t="n">
-        <v>9645831.756343259</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>PSSA_rm_FWD-rt3215</t>
-        </is>
-      </c>
-      <c r="B306" t="n">
-        <v>7142.137923422556</v>
-      </c>
-      <c r="C306" t="n">
-        <v>63329.57560262521</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>PYK_c_FWD-rt4634</t>
-        </is>
-      </c>
-      <c r="B307" t="n">
-        <v>1852523.275282805</v>
-      </c>
-      <c r="C307" t="n">
-        <v>105851.8284225916</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>PYRtps_m_FWD-MPC13</t>
-        </is>
-      </c>
-      <c r="B308" t="n">
-        <v>314030.9772923342</v>
-      </c>
-      <c r="C308" t="n">
-        <v>1413662.937461543</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>RBFK_c_FWD-rt0930_c</t>
-        </is>
-      </c>
-      <c r="B309" t="n">
-        <v>35.67006327169955</v>
-      </c>
-      <c r="C309" t="n">
-        <v>11.27850374583432</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>RLFC2O_c_FWD-rt4960</t>
-        </is>
-      </c>
-      <c r="B310" t="n">
-        <v>18568.45228640062</v>
-      </c>
-      <c r="C310" t="n">
-        <v>22482.5659771631</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>RLFC2O_m_FWD-rt8275</t>
-        </is>
-      </c>
-      <c r="B311" t="n">
-        <v>0.0347501948238189</v>
-      </c>
-      <c r="C311" t="n">
-        <v>2337.739368410757</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>RNDR1_c_FWD-RNR124</t>
-        </is>
-      </c>
-      <c r="B312" t="n">
-        <v>1338139.665315263</v>
-      </c>
-      <c r="C312" t="n">
-        <v>25908.18570643673</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>RNDR2_c_FWD-RNR124</t>
-        </is>
-      </c>
-      <c r="B313" t="n">
-        <v>1338139.665315263</v>
-      </c>
-      <c r="C313" t="n">
-        <v>25908.18570643673</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>RNDR3_c_FWD-RNR124</t>
-        </is>
-      </c>
-      <c r="B314" t="n">
-        <v>1338139.665315263</v>
-      </c>
-      <c r="C314" t="n">
-        <v>25908.18570643673</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>RPE_c_FWD-rt3505</t>
-        </is>
-      </c>
-      <c r="B315" t="n">
-        <v>208487.2424236492</v>
-      </c>
-      <c r="C315" t="n">
-        <v>931514.8389343416</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>RPE_c_FWD-rt7896</t>
-        </is>
-      </c>
-      <c r="B316" t="n">
-        <v>208487.2424236492</v>
-      </c>
-      <c r="C316" t="n">
-        <v>931514.8389343416</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>RPI_c_FWD-rt4920</t>
-        </is>
-      </c>
-      <c r="B317" t="n">
-        <v>164516.1608779297</v>
-      </c>
-      <c r="C317" t="n">
-        <v>348308.0184396874</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>SACCD1_c_FWD-rt8465</t>
-        </is>
-      </c>
-      <c r="B318" t="n">
-        <v>5174.934352000308</v>
-      </c>
-      <c r="C318" t="n">
-        <v>15104.35405866492</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>SACCD2_c_FWD-rt5719</t>
-        </is>
-      </c>
-      <c r="B319" t="n">
-        <v>11964.02100059462</v>
-      </c>
-      <c r="C319" t="n">
-        <v>4679.749446011388</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>SACCD2_c_FWD-rt8465</t>
-        </is>
-      </c>
-      <c r="B320" t="n">
-        <v>11964.02100059462</v>
-      </c>
-      <c r="C320" t="n">
-        <v>15104.35405866492</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>SADT_c_FWD-rt5075</t>
-        </is>
-      </c>
-      <c r="B321" t="n">
-        <v>15583.98616093314</v>
-      </c>
-      <c r="C321" t="n">
-        <v>20668.00320830337</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>SAM24MT_c_FWD-rt4692</t>
-        </is>
-      </c>
-      <c r="B322" t="n">
-        <v>867.9010017353328</v>
-      </c>
-      <c r="C322" t="n">
-        <v>6572.834013574188</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>SERAT_c_FWD-rt6880</t>
-        </is>
-      </c>
-      <c r="B323" t="n">
-        <v>23194.46883722087</v>
-      </c>
-      <c r="C323" t="n">
-        <v>175.9535161702319</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>SERTRS_c_FWD-rt1878</t>
-        </is>
-      </c>
-      <c r="B324" t="n">
-        <v>16073.67819388007</v>
-      </c>
-      <c r="C324" t="n">
-        <v>14721.10905009348</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>SERTRS_c_FWD-rt5857</t>
-        </is>
-      </c>
-      <c r="B325" t="n">
-        <v>16073.67819388007</v>
-      </c>
-      <c r="C325" t="n">
-        <v>14721.10905009348</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>SHK3Di_c_FWD-rt5884</t>
-        </is>
-      </c>
-      <c r="B326" t="n">
-        <v>265929.863259614</v>
-      </c>
-      <c r="C326" t="n">
-        <v>292550.0526924005</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>SHKK_c_FWD-rt5884</t>
-        </is>
-      </c>
-      <c r="B327" t="n">
-        <v>265929.863259614</v>
-      </c>
-      <c r="C327" t="n">
-        <v>292550.0526924005</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>SO3R_c_FWD-rt20063076</t>
-        </is>
-      </c>
-      <c r="B328" t="n">
-        <v>9980.836169543029</v>
-      </c>
-      <c r="C328" t="n">
-        <v>24405.43885139707</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>SO4t_c_e_FWD-rt7368</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>132289.7083084976</v>
-      </c>
-      <c r="C329" t="n">
-        <v>293368.1922639061</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>SSALy_c_FWD-rt0324</t>
-        </is>
-      </c>
-      <c r="B330" t="n">
-        <v>134568.4087664017</v>
-      </c>
-      <c r="C330" t="n">
-        <v>716.3544622556304</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>SSALy_c_FWD-rt8468</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>134568.4087664017</v>
-      </c>
-      <c r="C331" t="n">
-        <v>716.3544622556304</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>SUCCt2_m_FWD-rt5142</t>
-        </is>
-      </c>
-      <c r="B332" t="n">
-        <v>5853.936215493361</v>
-      </c>
-      <c r="C332" t="n">
-        <v>22482.5659771631</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>SUCOAS_m_FWD-LSC12</t>
-        </is>
-      </c>
-      <c r="B333" t="n">
-        <v>93890.19007389707</v>
-      </c>
-      <c r="C333" t="n">
-        <v>98536.10829205789</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>TALA_c_FWD-rt1805</t>
-        </is>
-      </c>
-      <c r="B334" t="n">
-        <v>35667.14969737249</v>
-      </c>
-      <c r="C334" t="n">
-        <v>13581.92532882125</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>THRD_L_m_FWD-rt0848_m</t>
-        </is>
-      </c>
-      <c r="B335" t="n">
-        <v>273968804381.2528</v>
-      </c>
-      <c r="C335" t="n">
-        <v>35476.19152349519</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>THRD_L_m_FWD-rt3541</t>
-        </is>
-      </c>
-      <c r="B336" t="n">
-        <v>273968804381.2528</v>
-      </c>
-      <c r="C336" t="n">
-        <v>35476.19152349519</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>THRS_c_FWD-rt1374</t>
-        </is>
-      </c>
-      <c r="B337" t="n">
-        <v>32807.9791964011</v>
-      </c>
-      <c r="C337" t="n">
-        <v>23669.24451345626</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>THRTRS_c_FWD-rt7480</t>
-        </is>
-      </c>
-      <c r="B338" t="n">
-        <v>12929.82164693064</v>
-      </c>
-      <c r="C338" t="n">
-        <v>15221.9279600001</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>TKT1_c_FWD-rt7263_c</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>1391006.830652197</v>
-      </c>
-      <c r="C339" t="n">
-        <v>171161.8786298099</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>TKT2_c_FWD-rt7263_c</t>
-        </is>
-      </c>
-      <c r="B340" t="n">
-        <v>1391006.830652197</v>
-      </c>
-      <c r="C340" t="n">
-        <v>171161.8786298099</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>TMDS_c_FWD-rt2477</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>1127.744227627963</v>
-      </c>
-      <c r="C341" t="n">
-        <v>976.237933691502</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>TPI_c_FWD-rt0932</t>
-        </is>
-      </c>
-      <c r="B342" t="n">
-        <v>517648.671547452</v>
-      </c>
-      <c r="C342" t="n">
-        <v>254798.1153765267</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>TRDR_c_FWD-rt1320</t>
-        </is>
-      </c>
-      <c r="B343" t="n">
-        <v>6943.233968803512</v>
-      </c>
-      <c r="C343" t="n">
-        <v>8420.1126749208</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>TRE6PP_c_FWD-TPS12TSL1</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>40162.1195092572</v>
-      </c>
-      <c r="C344" t="n">
-        <v>66475.92980683908</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>TRE6PS_c_FWD-TPS12TSL1</t>
-        </is>
-      </c>
-      <c r="B345" t="n">
-        <v>40162.1195092572</v>
-      </c>
-      <c r="C345" t="n">
-        <v>66475.92980683908</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>TRPO2_c_FWD-rt7555</t>
-        </is>
-      </c>
-      <c r="B346" t="n">
-        <v>582415.5758725944</v>
-      </c>
-      <c r="C346" t="n">
-        <v>991090025436.6539</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>TRPS1_c_FWD-rt0894</t>
-        </is>
-      </c>
-      <c r="B347" t="n">
-        <v>14929.45851275327</v>
-      </c>
-      <c r="C347" t="n">
-        <v>11242.8082144755</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>TRPTRS_c_FWD-rt6341</t>
-        </is>
-      </c>
-      <c r="B348" t="n">
-        <v>8968.764818613025</v>
-      </c>
-      <c r="C348" t="n">
-        <v>3517.035982603905</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>TYRTA_c_FWD-rt7471</t>
-        </is>
-      </c>
-      <c r="B349" t="n">
-        <v>61343.54779923144</v>
-      </c>
-      <c r="C349" t="n">
-        <v>417809.4145928964</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>TYRTA_c_FWD-rt7697</t>
-        </is>
-      </c>
-      <c r="B350" t="n">
-        <v>61343.54779923144</v>
-      </c>
-      <c r="C350" t="n">
-        <v>22673.76654537086</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>TYRTRS_c_FWD-rt8273</t>
-        </is>
-      </c>
-      <c r="B351" t="n">
-        <v>19825.3748843906</v>
-      </c>
-      <c r="C351" t="n">
-        <v>10461.04264667272</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>UAGDP_c_FWD-rt0711</t>
-        </is>
-      </c>
-      <c r="B352" t="n">
-        <v>3645.33825492108</v>
-      </c>
-      <c r="C352" t="n">
-        <v>1724.906577907145</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>UMPK_c_FWD-rt4822_c</t>
-        </is>
-      </c>
-      <c r="B353" t="n">
-        <v>26876.92699492516</v>
-      </c>
-      <c r="C353" t="n">
-        <v>30321.07322466787</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>UPP3S_c_FWD-rt2147</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>26.261986486163</v>
-      </c>
-      <c r="C354" t="n">
-        <v>413528604.572286</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>VALTA_c_FWD-rt5646</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>3039403.4909217</v>
-      </c>
-      <c r="C355" t="n">
-        <v>717080.4180638532</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>VALTA_m_REV-rt6242_m</t>
-        </is>
-      </c>
-      <c r="B356" t="n">
-        <v>47302.57888388856</v>
-      </c>
-      <c r="C356" t="n">
-        <v>59914.79594089955</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>VALTRS_c_FWD-rt8160_c</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>18299.22961483771</v>
-      </c>
-      <c r="C357" t="n">
-        <v>27666.46299140773</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>YUMPS_c_REV-rt6068</t>
-        </is>
-      </c>
-      <c r="B358" t="n">
-        <v>2.005425259137803e-12</v>
-      </c>
-      <c r="C358" t="n">
-        <v>2.664581778344966e-12</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>YUMPS_c_REV-rt7720</t>
-        </is>
-      </c>
-      <c r="B359" t="n">
-        <v>2.005425259137803e-12</v>
-      </c>
-      <c r="C359" t="n">
-        <v>2.664581778344966e-12</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>YUMPS_c_REV-rt8055</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>2.005425259137803e-12</v>
-      </c>
-      <c r="C360" t="n">
-        <v>2.664581778344966e-12</v>
+        <v>1.332290889172484e-12</v>
       </c>
     </row>
   </sheetData>
